--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HetalJethva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AF0ADE-22E7-429A-AFCB-2392A14BB6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7088AAF5-77A2-454F-AE9C-E92E5D6ED3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A07144B-59AD-4B98-9627-376AA969DDF8}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="482">
   <si>
     <t>Customer Label</t>
   </si>
@@ -1615,7 +1615,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1676,18 +1676,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3236,7 +3234,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
         <v>101</v>
       </c>
@@ -3758,7 +3756,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>129</v>
       </c>
@@ -4929,7 +4927,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A162" s="26" t="s">
+      <c r="A162" s="25" t="s">
         <v>199</v>
       </c>
       <c r="B162" s="4" t="s">
@@ -4965,7 +4963,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A164" s="26" t="s">
+      <c r="A164" s="25" t="s">
         <v>201</v>
       </c>
       <c r="B164" s="4" t="s">
@@ -5055,7 +5053,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A169" s="26" t="s">
+      <c r="A169" s="25" t="s">
         <v>207</v>
       </c>
       <c r="B169" s="4" t="s">
@@ -5144,7 +5142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="10" t="s">
         <v>212</v>
       </c>
@@ -5360,7 +5358,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="10" t="s">
         <v>226</v>
       </c>
@@ -6441,7 +6439,7 @@
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A246" s="27" t="s">
+      <c r="A246" s="6" t="s">
         <v>288</v>
       </c>
       <c r="B246" s="20" t="s">
@@ -6454,7 +6452,7 @@
       <c r="D246" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E246" s="27" t="s">
+      <c r="E246" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -6477,7 +6475,7 @@
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A248" s="27" t="s">
+      <c r="A248" s="6" t="s">
         <v>290</v>
       </c>
       <c r="B248" s="20" t="s">
@@ -6490,7 +6488,7 @@
       <c r="D248" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E248" s="27" t="s">
+      <c r="E248" s="6" t="s">
         <v>171</v>
       </c>
     </row>
@@ -6549,7 +6547,7 @@
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A252" s="27" t="s">
+      <c r="A252" s="6" t="s">
         <v>294</v>
       </c>
       <c r="B252" s="20" t="s">
@@ -6562,7 +6560,7 @@
       <c r="D252" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E252" s="27" t="s">
+      <c r="E252" s="6" t="s">
         <v>295</v>
       </c>
     </row>
@@ -6603,7 +6601,7 @@
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A255" s="27" t="s">
+      <c r="A255" s="6" t="s">
         <v>298</v>
       </c>
       <c r="B255" s="20" t="s">
@@ -6616,7 +6614,7 @@
       <c r="D255" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E255" s="27" t="s">
+      <c r="E255" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -6675,7 +6673,7 @@
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A259" s="27" t="s">
+      <c r="A259" s="6" t="s">
         <v>302</v>
       </c>
       <c r="B259" s="4" t="s">
@@ -6688,7 +6686,7 @@
       <c r="D259" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E259" s="27" t="s">
+      <c r="E259" s="6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -6747,7 +6745,7 @@
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A263" s="27" t="s">
+      <c r="A263" s="6" t="s">
         <v>306</v>
       </c>
       <c r="B263" s="20" t="s">
@@ -6760,7 +6758,7 @@
       <c r="D263" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E263" s="27" t="s">
+      <c r="E263" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -6837,7 +6835,7 @@
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A268" s="27" t="s">
+      <c r="A268" s="6" t="s">
         <v>311</v>
       </c>
       <c r="B268" s="20" t="s">
@@ -6850,12 +6848,12 @@
       <c r="D268" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E268" s="27" t="s">
+      <c r="E268" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A269" s="27" t="s">
+      <c r="A269" s="6" t="s">
         <v>311</v>
       </c>
       <c r="B269" s="20" t="s">
@@ -6868,7 +6866,7 @@
       <c r="D269" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E269" s="27" t="s">
+      <c r="E269" s="6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -7179,7 +7177,7 @@
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A287" s="27" t="s">
+      <c r="A287" s="6" t="s">
         <v>328</v>
       </c>
       <c r="B287" s="20" t="s">
@@ -7192,7 +7190,7 @@
       <c r="D287" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E287" s="27" t="s">
+      <c r="E287" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7305,7 +7303,7 @@
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A294" s="27" t="s">
+      <c r="A294" s="6" t="s">
         <v>335</v>
       </c>
       <c r="B294" s="20" t="s">
@@ -7318,12 +7316,12 @@
       <c r="D294" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E294" s="27" t="s">
+      <c r="E294" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A295" s="27" t="s">
+      <c r="A295" s="6" t="s">
         <v>336</v>
       </c>
       <c r="B295" s="4" t="s">
@@ -7336,12 +7334,12 @@
       <c r="D295" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E295" s="27" t="s">
+      <c r="E295" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A296" s="27" t="s">
+      <c r="A296" s="6" t="s">
         <v>337</v>
       </c>
       <c r="B296" s="20" t="s">
@@ -7354,12 +7352,12 @@
       <c r="D296" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E296" s="27" t="s">
+      <c r="E296" s="6" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A297" s="27" t="s">
+      <c r="A297" s="6" t="s">
         <v>338</v>
       </c>
       <c r="B297" s="20" t="s">
@@ -7372,7 +7370,7 @@
       <c r="D297" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E297" s="27" t="s">
+      <c r="E297" s="6" t="s">
         <v>126</v>
       </c>
     </row>
@@ -7462,7 +7460,7 @@
       <c r="D302" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E302" s="27" t="s">
+      <c r="E302" s="6" t="s">
         <v>344</v>
       </c>
     </row>
@@ -7480,7 +7478,7 @@
       <c r="D303" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E303" s="27" t="s">
+      <c r="E303" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -7534,7 +7532,7 @@
       <c r="D306" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E306" s="27" t="s">
+      <c r="E306" s="6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7683,7 +7681,7 @@
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A315" s="27" t="s">
+      <c r="A315" s="6" t="s">
         <v>356</v>
       </c>
       <c r="B315" s="4" t="s">
@@ -7696,12 +7694,12 @@
       <c r="D315" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E315" s="27" t="s">
+      <c r="E315" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A316" s="27" t="s">
+      <c r="A316" s="6" t="s">
         <v>357</v>
       </c>
       <c r="B316" s="4" t="s">
@@ -7714,12 +7712,12 @@
       <c r="D316" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E316" s="27" t="s">
+      <c r="E316" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A317" s="27" t="s">
+      <c r="A317" s="6" t="s">
         <v>358</v>
       </c>
       <c r="B317" s="4" t="s">
@@ -7732,12 +7730,12 @@
       <c r="D317" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E317" s="27" t="s">
+      <c r="E317" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A318" s="27" t="s">
+      <c r="A318" s="6" t="s">
         <v>359</v>
       </c>
       <c r="B318" s="20" t="s">
@@ -7750,7 +7748,7 @@
       <c r="D318" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E318" s="27" t="s">
+      <c r="E318" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7768,7 +7766,7 @@
       <c r="D319" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E319" s="27" t="s">
+      <c r="E319" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7804,7 +7802,7 @@
       <c r="D321" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E321" s="27" t="s">
+      <c r="E321" s="6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7863,7 +7861,7 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A325" s="27" t="s">
+      <c r="A325" s="6" t="s">
         <v>366</v>
       </c>
       <c r="B325" s="20" t="s">
@@ -7876,12 +7874,12 @@
       <c r="D325" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E325" s="27" t="s">
+      <c r="E325" s="6" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A326" s="27" t="s">
+      <c r="A326" s="6" t="s">
         <v>368</v>
       </c>
       <c r="B326" s="4" t="s">
@@ -7894,12 +7892,12 @@
       <c r="D326" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E326" s="27" t="s">
+      <c r="E326" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A327" s="27" t="s">
+      <c r="A327" s="6" t="s">
         <v>369</v>
       </c>
       <c r="B327" s="4" t="s">
@@ -7912,12 +7910,12 @@
       <c r="D327" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E327" s="27" t="s">
+      <c r="E327" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A328" s="27" t="s">
+      <c r="A328" s="6" t="s">
         <v>370</v>
       </c>
       <c r="B328" s="4" t="s">
@@ -7930,12 +7928,12 @@
       <c r="D328" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E328" s="27" t="s">
+      <c r="E328" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A329" s="27" t="s">
+      <c r="A329" s="6" t="s">
         <v>371</v>
       </c>
       <c r="B329" s="20" t="s">
@@ -7948,12 +7946,12 @@
       <c r="D329" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E329" s="27" t="s">
+      <c r="E329" s="6" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A330" s="27" t="s">
+      <c r="A330" s="6" t="s">
         <v>372</v>
       </c>
       <c r="B330" s="4" t="s">
@@ -7966,7 +7964,7 @@
       <c r="D330" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E330" s="27" t="s">
+      <c r="E330" s="6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -8061,7 +8059,7 @@
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A336" s="27" t="s">
+      <c r="A336" s="6" t="s">
         <v>379</v>
       </c>
       <c r="B336" s="20" t="s">
@@ -8074,12 +8072,12 @@
       <c r="D336" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E336" s="27" t="s">
+      <c r="E336" s="6" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A337" s="27" t="s">
+      <c r="A337" s="6" t="s">
         <v>381</v>
       </c>
       <c r="B337" s="20" t="s">
@@ -8092,12 +8090,12 @@
       <c r="D337" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E337" s="27" t="s">
+      <c r="E337" s="6" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A338" s="27" t="s">
+      <c r="A338" s="6" t="s">
         <v>381</v>
       </c>
       <c r="B338" s="20" t="s">
@@ -8110,7 +8108,7 @@
       <c r="D338" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E338" s="27" t="s">
+      <c r="E338" s="6" t="s">
         <v>382</v>
       </c>
     </row>
@@ -8133,7 +8131,7 @@
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A340" s="27" t="s">
+      <c r="A340" s="6" t="s">
         <v>384</v>
       </c>
       <c r="B340" s="4" t="s">
@@ -8146,7 +8144,7 @@
       <c r="D340" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E340" s="27" t="s">
+      <c r="E340" s="6" t="s">
         <v>375</v>
       </c>
     </row>
@@ -8238,10 +8236,10 @@
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A346" s="25" t="s">
+      <c r="A346" t="s">
         <v>390</v>
       </c>
-      <c r="B346" s="25" t="s">
+      <c r="B346" t="s">
         <v>38</v>
       </c>
       <c r="C346" s="4" t="str">
@@ -8251,19 +8249,17 @@
       <c r="D346" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E346" s="25"/>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>391</v>
       </c>
-      <c r="B347" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C347" s="4" t="e">
+      <c r="B347" t="s">
+        <v>34</v>
+      </c>
+      <c r="C347" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>#REF!</v>
+        <v>MEA</v>
       </c>
       <c r="D347" s="22" t="s">
         <v>35</v>
@@ -8276,13 +8272,12 @@
       <c r="A348" t="s">
         <v>392</v>
       </c>
-      <c r="B348" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C348" s="4" t="e">
+      <c r="B348" t="s">
+        <v>10</v>
+      </c>
+      <c r="C348" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>#REF!</v>
+        <v>Americas</v>
       </c>
       <c r="D348" s="22" t="s">
         <v>190</v>
@@ -8499,13 +8494,12 @@
       <c r="A362" t="s">
         <v>406</v>
       </c>
-      <c r="B362" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C362" s="4" t="e">
+      <c r="B362" t="s">
+        <v>34</v>
+      </c>
+      <c r="C362" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>#REF!</v>
+        <v>MEA</v>
       </c>
       <c r="D362" s="22" t="s">
         <v>35</v>
@@ -8551,13 +8545,12 @@
       <c r="A365" t="s">
         <v>409</v>
       </c>
-      <c r="B365" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C365" s="4" t="e">
+      <c r="B365" t="s">
+        <v>10</v>
+      </c>
+      <c r="C365" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>#REF!</v>
+        <v>Americas</v>
       </c>
       <c r="D365" s="22" t="s">
         <v>190</v>
@@ -8582,23 +8575,22 @@
       <c r="A367" t="s">
         <v>411</v>
       </c>
-      <c r="B367" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C367" s="4" t="e">
+      <c r="B367" t="s">
+        <v>10</v>
+      </c>
+      <c r="C367" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>#REF!</v>
+        <v>Americas</v>
       </c>
       <c r="D367" s="22" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A368" s="25" t="s">
+      <c r="A368" t="s">
         <v>412</v>
       </c>
-      <c r="B368" s="25" t="s">
+      <c r="B368" t="s">
         <v>38</v>
       </c>
       <c r="C368" s="4" t="str">
@@ -8608,7 +8600,6 @@
       <c r="D368" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E368" s="25"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
@@ -8641,20 +8632,19 @@
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A371" s="25" t="s">
+      <c r="A371" t="s">
         <v>415</v>
       </c>
-      <c r="B371" s="25" t="s">
+      <c r="B371" t="s">
         <v>38</v>
       </c>
       <c r="C371" s="4" t="str">
         <f t="shared" si="5"/>
         <v>SME</v>
       </c>
-      <c r="D371" s="25" t="s">
+      <c r="D371" t="s">
         <v>476</v>
       </c>
-      <c r="E371" s="25"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
@@ -8909,10 +8899,10 @@
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A388" s="25" t="s">
+      <c r="A388" t="s">
         <v>432</v>
       </c>
-      <c r="B388" s="25" t="s">
+      <c r="B388" t="s">
         <v>10</v>
       </c>
       <c r="C388" s="4" t="str">
@@ -8922,15 +8912,15 @@
       <c r="D388" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E388" s="25" t="s">
+      <c r="E388" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A389" s="25" t="s">
+      <c r="A389" t="s">
         <v>433</v>
       </c>
-      <c r="B389" s="25" t="s">
+      <c r="B389" t="s">
         <v>10</v>
       </c>
       <c r="C389" s="4" t="str">
@@ -8940,7 +8930,6 @@
       <c r="D389" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E389" s="25"/>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
@@ -8976,26 +8965,25 @@
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A392" s="25" t="s">
+      <c r="A392" t="s">
         <v>436</v>
       </c>
-      <c r="B392" s="25" t="s">
+      <c r="B392" t="s">
         <v>38</v>
       </c>
       <c r="C392" s="4" t="str">
         <f t="shared" si="6"/>
         <v>SME</v>
       </c>
-      <c r="D392" s="25" t="s">
+      <c r="D392" t="s">
         <v>476</v>
       </c>
-      <c r="E392" s="25"/>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A393" s="25" t="s">
+      <c r="A393" t="s">
         <v>437</v>
       </c>
-      <c r="B393" s="25" t="s">
+      <c r="B393" t="s">
         <v>10</v>
       </c>
       <c r="C393" s="4" t="str">
@@ -9005,15 +8993,15 @@
       <c r="D393" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E393" s="25" t="s">
+      <c r="E393" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A394" s="25" t="s">
+      <c r="A394" t="s">
         <v>438</v>
       </c>
-      <c r="B394" s="25" t="s">
+      <c r="B394" t="s">
         <v>10</v>
       </c>
       <c r="C394" s="4" t="str">
@@ -9023,22 +9011,22 @@
       <c r="D394" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E394" s="25" t="s">
+      <c r="E394" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A395" s="25" t="s">
+      <c r="A395" t="s">
         <v>439</v>
       </c>
-      <c r="B395" s="25" t="s">
+      <c r="B395" t="s">
         <v>6</v>
       </c>
       <c r="C395" s="4" t="str">
         <f t="shared" si="6"/>
         <v>APAC</v>
       </c>
-      <c r="D395" s="25" t="s">
+      <c r="D395" t="s">
         <v>476</v>
       </c>
       <c r="E395" s="5" t="s">
@@ -9049,13 +9037,12 @@
       <c r="A396" t="s">
         <v>440</v>
       </c>
-      <c r="B396" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C396" s="4" t="e">
+      <c r="B396" t="s">
+        <v>34</v>
+      </c>
+      <c r="C396" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>#REF!</v>
+        <v>MEA</v>
       </c>
       <c r="D396" s="22" t="s">
         <v>35</v>
@@ -9083,10 +9070,10 @@
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A398" s="25" t="s">
+      <c r="A398" t="s">
         <v>442</v>
       </c>
-      <c r="B398" s="25" t="s">
+      <c r="B398" t="s">
         <v>10</v>
       </c>
       <c r="C398" s="4" t="str">
@@ -9096,22 +9083,22 @@
       <c r="D398" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E398" s="25" t="s">
+      <c r="E398" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A399" s="25" t="s">
+      <c r="A399" t="s">
         <v>443</v>
       </c>
-      <c r="B399" s="25" t="s">
+      <c r="B399" t="s">
         <v>6</v>
       </c>
       <c r="C399" s="4" t="str">
         <f t="shared" si="6"/>
         <v>APAC</v>
       </c>
-      <c r="D399" s="25" t="s">
+      <c r="D399" t="s">
         <v>476</v>
       </c>
       <c r="E399" s="5" t="s">
@@ -9149,10 +9136,10 @@
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A402" s="25" t="s">
+      <c r="A402" t="s">
         <v>446</v>
       </c>
-      <c r="B402" s="25" t="s">
+      <c r="B402" t="s">
         <v>10</v>
       </c>
       <c r="C402" s="4" t="str">
@@ -9162,7 +9149,7 @@
       <c r="D402" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E402" s="25" t="s">
+      <c r="E402" t="s">
         <v>58</v>
       </c>
     </row>
@@ -9203,7 +9190,7 @@
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A405" s="25" t="s">
+      <c r="A405" t="s">
         <v>449</v>
       </c>
       <c r="B405" s="4" t="s">
@@ -9213,10 +9200,10 @@
         <f t="shared" si="6"/>
         <v>EU/UK</v>
       </c>
-      <c r="D405" s="25" t="s">
+      <c r="D405" t="s">
         <v>476</v>
       </c>
-      <c r="E405" s="25" t="s">
+      <c r="E405" t="s">
         <v>477</v>
       </c>
     </row>
@@ -9236,21 +9223,19 @@
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A407" s="25" t="s">
+      <c r="A407" t="s">
         <v>451</v>
       </c>
-      <c r="B407" s="25" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C407" s="4" t="e">
+      <c r="B407" t="s">
+        <v>10</v>
+      </c>
+      <c r="C407" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>#REF!</v>
+        <v>Americas</v>
       </c>
       <c r="D407" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E407" s="25"/>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
@@ -9370,20 +9355,19 @@
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A415" s="25" t="s">
+      <c r="A415" t="s">
         <v>459</v>
       </c>
-      <c r="B415" s="25" t="s">
+      <c r="B415" t="s">
         <v>6</v>
       </c>
       <c r="C415" s="4" t="str">
         <f t="shared" si="6"/>
         <v>APAC</v>
       </c>
-      <c r="D415" s="25" t="s">
+      <c r="D415" t="s">
         <v>476</v>
       </c>
-      <c r="E415" s="25"/>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
@@ -9488,20 +9472,19 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A422" s="25" t="s">
+      <c r="A422" t="s">
         <v>466</v>
       </c>
-      <c r="B422" s="25" t="s">
+      <c r="B422" t="s">
         <v>38</v>
       </c>
       <c r="C422" s="4" t="str">
         <f t="shared" si="6"/>
         <v>SME</v>
       </c>
-      <c r="D422" s="25" t="s">
+      <c r="D422" t="s">
         <v>476</v>
       </c>
-      <c r="E422" s="25"/>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
@@ -9549,52 +9532,49 @@
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A426" s="25" t="s">
+      <c r="A426" t="s">
         <v>470</v>
       </c>
-      <c r="B426" s="25" t="s">
+      <c r="B426" t="s">
         <v>38</v>
       </c>
       <c r="C426" s="4" t="str">
         <f t="shared" si="6"/>
         <v>SME</v>
       </c>
-      <c r="D426" s="25" t="s">
+      <c r="D426" t="s">
         <v>476</v>
       </c>
-      <c r="E426" s="25"/>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A427" s="25" t="s">
+      <c r="A427" t="s">
         <v>471</v>
       </c>
-      <c r="B427" s="25" t="s">
+      <c r="B427" t="s">
         <v>10</v>
       </c>
       <c r="C427" s="4" t="str">
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D427" s="25" t="s">
+      <c r="D427" t="s">
         <v>11</v>
       </c>
-      <c r="E427" s="25"/>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A428" s="25" t="s">
+      <c r="A428" t="s">
         <v>472</v>
       </c>
-      <c r="B428" s="25" t="s">
+      <c r="B428" t="s">
         <v>38</v>
       </c>
       <c r="C428" s="4" t="str">
         <f t="shared" si="6"/>
         <v>SME</v>
       </c>
-      <c r="D428" s="25" t="s">
+      <c r="D428" t="s">
         <v>476</v>
       </c>
-      <c r="E428" s="25"/>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A429" t="s">

--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HetalJethva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7088AAF5-77A2-454F-AE9C-E92E5D6ED3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777E1A11-E2DA-45EE-8DAA-7369ADEADD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A07144B-59AD-4B98-9627-376AA969DDF8}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="484">
   <si>
     <t>Customer Label</t>
   </si>
@@ -1488,13 +1488,19 @@
   </si>
   <si>
     <t xml:space="preserve"> Simrn Gandhi</t>
+  </si>
+  <si>
+    <t>Relay Financial (US), Corp</t>
+  </si>
+  <si>
+    <t>REHABILITATION DEBTOR MTGOX CO. LTD AND REHABILITATION TRUSTEE AND ATTORNEY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1553,6 +1559,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF1E293B"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1574,7 +1586,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1608,6 +1620,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1615,7 +1636,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1686,6 +1707,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2023,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0576E467-0835-47AC-A23C-AF9DB748328C}">
-  <dimension ref="A1:E431"/>
+  <dimension ref="A1:E433"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="1"/>
@@ -2208,7 +2234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
@@ -2226,7 +2252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -2244,7 +2270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -2262,7 +2288,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -2280,7 +2306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
@@ -2298,7 +2324,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
@@ -2316,7 +2342,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -2334,7 +2360,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
@@ -2352,7 +2378,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
@@ -2370,7 +2396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
@@ -2388,7 +2414,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
@@ -2406,7 +2432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
@@ -2424,7 +2450,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>46</v>
       </c>
@@ -2442,7 +2468,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>47</v>
       </c>
@@ -2460,7 +2486,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -2478,7 +2504,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
@@ -2514,7 +2540,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>51</v>
       </c>
@@ -2532,7 +2558,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>52</v>
       </c>
@@ -2568,7 +2594,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
         <v>55</v>
       </c>
@@ -2586,7 +2612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>57</v>
       </c>
@@ -2604,7 +2630,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>59</v>
       </c>
@@ -2622,7 +2648,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>60</v>
       </c>
@@ -2640,7 +2666,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>62</v>
       </c>
@@ -2658,7 +2684,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>64</v>
       </c>
@@ -2694,7 +2720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>66</v>
       </c>
@@ -2712,7 +2738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>68</v>
       </c>
@@ -2730,7 +2756,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>69</v>
       </c>
@@ -2748,7 +2774,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>70</v>
       </c>
@@ -2766,7 +2792,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
         <v>72</v>
       </c>
@@ -2802,7 +2828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>75</v>
       </c>
@@ -2820,7 +2846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>76</v>
       </c>
@@ -2838,7 +2864,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="14" t="s">
         <v>78</v>
       </c>
@@ -2856,7 +2882,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
         <v>59</v>
       </c>
@@ -2874,7 +2900,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>82</v>
       </c>
@@ -2892,7 +2918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
         <v>83</v>
       </c>
@@ -2910,7 +2936,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
         <v>84</v>
       </c>
@@ -2928,7 +2954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
         <v>85</v>
       </c>
@@ -2946,7 +2972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>86</v>
       </c>
@@ -2964,7 +2990,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
         <v>87</v>
       </c>
@@ -2982,7 +3008,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
         <v>89</v>
       </c>
@@ -3000,7 +3026,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>90</v>
       </c>
@@ -3018,7 +3044,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="14" t="s">
         <v>91</v>
       </c>
@@ -3036,7 +3062,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="14" t="s">
         <v>45</v>
       </c>
@@ -3054,7 +3080,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="14" t="s">
         <v>92</v>
       </c>
@@ -3072,7 +3098,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="14" t="s">
         <v>93</v>
       </c>
@@ -3090,7 +3116,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>94</v>
       </c>
@@ -3108,7 +3134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
         <v>95</v>
       </c>
@@ -3126,7 +3152,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>60</v>
       </c>
@@ -3144,7 +3170,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="14" t="s">
         <v>97</v>
       </c>
@@ -3162,7 +3188,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>62</v>
       </c>
@@ -3180,7 +3206,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>47</v>
       </c>
@@ -3198,7 +3224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
         <v>99</v>
       </c>
@@ -3216,7 +3242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
         <v>100</v>
       </c>
@@ -3252,7 +3278,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
         <v>102</v>
       </c>
@@ -3270,7 +3296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>103</v>
       </c>
@@ -3288,7 +3314,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
         <v>28</v>
       </c>
@@ -3306,7 +3332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
         <v>104</v>
       </c>
@@ -3324,7 +3350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>105</v>
       </c>
@@ -3342,7 +3368,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="14" t="s">
         <v>107</v>
       </c>
@@ -3360,7 +3386,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
         <v>108</v>
       </c>
@@ -3378,7 +3404,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
         <v>29</v>
       </c>
@@ -3396,7 +3422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
         <v>49</v>
       </c>
@@ -3414,7 +3440,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
         <v>109</v>
       </c>
@@ -3432,7 +3458,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>111</v>
       </c>
@@ -3468,7 +3494,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>113</v>
       </c>
@@ -3486,7 +3512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>114</v>
       </c>
@@ -3504,7 +3530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>115</v>
       </c>
@@ -3558,7 +3584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>117</v>
       </c>
@@ -3612,7 +3638,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>122</v>
       </c>
@@ -3630,7 +3656,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>51</v>
       </c>
@@ -3648,7 +3674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>124</v>
       </c>
@@ -3666,7 +3692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>125</v>
       </c>
@@ -3684,7 +3710,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>127</v>
       </c>
@@ -3702,7 +3728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>52</v>
       </c>
@@ -3720,7 +3746,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>33</v>
       </c>
@@ -3738,7 +3764,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>128</v>
       </c>
@@ -3774,7 +3800,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>131</v>
       </c>
@@ -3792,7 +3818,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>132</v>
       </c>
@@ -3828,7 +3854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>133</v>
       </c>
@@ -3846,7 +3872,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>134</v>
       </c>
@@ -3864,7 +3890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>135</v>
       </c>
@@ -3882,7 +3908,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>136</v>
       </c>
@@ -3900,7 +3926,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>137</v>
       </c>
@@ -3918,7 +3944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>138</v>
       </c>
@@ -3936,7 +3962,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>139</v>
       </c>
@@ -3954,7 +3980,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
         <v>140</v>
       </c>
@@ -3972,7 +3998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>141</v>
       </c>
@@ -3990,7 +4016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>142</v>
       </c>
@@ -4008,7 +4034,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>143</v>
       </c>
@@ -4026,7 +4052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
         <v>144</v>
       </c>
@@ -4080,7 +4106,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>147</v>
       </c>
@@ -4098,7 +4124,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>148</v>
       </c>
@@ -4116,7 +4142,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
         <v>149</v>
       </c>
@@ -4134,7 +4160,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
         <v>150</v>
       </c>
@@ -4152,7 +4178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
         <v>151</v>
       </c>
@@ -4170,7 +4196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
         <v>152</v>
       </c>
@@ -4188,7 +4214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>153</v>
       </c>
@@ -4206,7 +4232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>154</v>
       </c>
@@ -4224,7 +4250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>154</v>
       </c>
@@ -4260,7 +4286,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>156</v>
       </c>
@@ -4278,7 +4304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>157</v>
       </c>
@@ -4296,7 +4322,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
         <v>158</v>
       </c>
@@ -4314,7 +4340,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
         <v>159</v>
       </c>
@@ -4350,7 +4376,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
         <v>161</v>
       </c>
@@ -4368,7 +4394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
         <v>162</v>
       </c>
@@ -4386,7 +4412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
         <v>163</v>
       </c>
@@ -4404,7 +4430,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
         <v>164</v>
       </c>
@@ -4422,7 +4448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
         <v>165</v>
       </c>
@@ -4440,7 +4466,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
         <v>166</v>
       </c>
@@ -4458,7 +4484,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
         <v>167</v>
       </c>
@@ -4476,7 +4502,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>169</v>
       </c>
@@ -4530,7 +4556,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="10" t="s">
         <v>173</v>
       </c>
@@ -4548,7 +4574,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="10" t="s">
         <v>175</v>
       </c>
@@ -4566,7 +4592,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="10" t="s">
         <v>176</v>
       </c>
@@ -4602,7 +4628,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>178</v>
       </c>
@@ -4620,7 +4646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>179</v>
       </c>
@@ -4638,7 +4664,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
         <v>180</v>
       </c>
@@ -4746,7 +4772,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
         <v>187</v>
       </c>
@@ -4782,7 +4808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
         <v>189</v>
       </c>
@@ -4818,7 +4844,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
         <v>192</v>
       </c>
@@ -4836,7 +4862,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>193</v>
       </c>
@@ -4872,7 +4898,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
         <v>195</v>
       </c>
@@ -4908,7 +4934,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
         <v>198</v>
       </c>
@@ -4944,7 +4970,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="17" t="s">
         <v>200</v>
       </c>
@@ -4980,7 +5006,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="17" t="s">
         <v>202</v>
       </c>
@@ -4998,7 +5024,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="17" t="s">
         <v>204</v>
       </c>
@@ -5016,7 +5042,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="17" t="s">
         <v>205</v>
       </c>
@@ -5034,7 +5060,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="17" t="s">
         <v>206</v>
       </c>
@@ -5088,7 +5114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="10" t="s">
         <v>209</v>
       </c>
@@ -5106,7 +5132,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="10" t="s">
         <v>210</v>
       </c>
@@ -5124,7 +5150,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="10" t="s">
         <v>211</v>
       </c>
@@ -5178,7 +5204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="10" t="s">
         <v>214</v>
       </c>
@@ -5232,7 +5258,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>217</v>
       </c>
@@ -5250,7 +5276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
         <v>219</v>
       </c>
@@ -5268,7 +5294,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="10" t="s">
         <v>220</v>
       </c>
@@ -5286,7 +5312,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="10" t="s">
         <v>222</v>
       </c>
@@ -5304,7 +5330,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="10" t="s">
         <v>223</v>
       </c>
@@ -5322,7 +5348,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="10" t="s">
         <v>224</v>
       </c>
@@ -5340,7 +5366,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="10" t="s">
         <v>225</v>
       </c>
@@ -5376,7 +5402,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="10" t="s">
         <v>227</v>
       </c>
@@ -5394,7 +5420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="10" t="s">
         <v>228</v>
       </c>
@@ -5412,7 +5438,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="10" t="s">
         <v>229</v>
       </c>
@@ -5430,7 +5456,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="10" t="s">
         <v>230</v>
       </c>
@@ -5448,7 +5474,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="10" t="s">
         <v>231</v>
       </c>
@@ -5466,7 +5492,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="10" t="s">
         <v>232</v>
       </c>
@@ -5502,7 +5528,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
         <v>235</v>
       </c>
@@ -5538,7 +5564,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
         <v>237</v>
       </c>
@@ -5556,7 +5582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>238</v>
       </c>
@@ -5574,7 +5600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
         <v>239</v>
       </c>
@@ -5592,7 +5618,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="10" t="s">
         <v>240</v>
       </c>
@@ -5610,7 +5636,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="10" t="s">
         <v>241</v>
       </c>
@@ -5628,7 +5654,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="10" t="s">
         <v>242</v>
       </c>
@@ -5646,7 +5672,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="10" t="s">
         <v>243</v>
       </c>
@@ -5664,7 +5690,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="10" t="s">
         <v>244</v>
       </c>
@@ -5682,7 +5708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="10" t="s">
         <v>245</v>
       </c>
@@ -5700,7 +5726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="14" t="s">
         <v>246</v>
       </c>
@@ -5754,7 +5780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="10" t="s">
         <v>249</v>
       </c>
@@ -5772,7 +5798,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="10" t="s">
         <v>250</v>
       </c>
@@ -5826,7 +5852,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="10" t="s">
         <v>253</v>
       </c>
@@ -5862,7 +5888,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A214" s="10" t="s">
         <v>255</v>
       </c>
@@ -5880,7 +5906,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="10" t="s">
         <v>256</v>
       </c>
@@ -5898,7 +5924,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="10" t="s">
         <v>257</v>
       </c>
@@ -5916,7 +5942,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="10" t="s">
         <v>258</v>
       </c>
@@ -5934,7 +5960,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="10" t="s">
         <v>259</v>
       </c>
@@ -5952,7 +5978,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="10" t="s">
         <v>260</v>
       </c>
@@ -5970,7 +5996,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A220" s="10" t="s">
         <v>261</v>
       </c>
@@ -6006,7 +6032,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="10" t="s">
         <v>263</v>
       </c>
@@ -6024,7 +6050,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="10" t="s">
         <v>264</v>
       </c>
@@ -6042,7 +6068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="10" t="s">
         <v>265</v>
       </c>
@@ -6060,7 +6086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="10" t="s">
         <v>266</v>
       </c>
@@ -6078,7 +6104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
         <v>267</v>
       </c>
@@ -6096,7 +6122,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="10" t="s">
         <v>268</v>
       </c>
@@ -6114,7 +6140,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
         <v>269</v>
       </c>
@@ -6132,7 +6158,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="10" t="s">
         <v>270</v>
       </c>
@@ -6150,7 +6176,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
         <v>271</v>
       </c>
@@ -6168,7 +6194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="10" t="s">
         <v>272</v>
       </c>
@@ -6186,7 +6212,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
         <v>273</v>
       </c>
@@ -6240,7 +6266,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="10" t="s">
         <v>276</v>
       </c>
@@ -6258,7 +6284,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
         <v>277</v>
       </c>
@@ -6276,7 +6302,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="10" t="s">
         <v>278</v>
       </c>
@@ -6294,7 +6320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="14" t="s">
         <v>279</v>
       </c>
@@ -6312,7 +6338,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="14" t="s">
         <v>280</v>
       </c>
@@ -6330,7 +6356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="14" t="s">
         <v>281</v>
       </c>
@@ -6348,7 +6374,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="14" t="s">
         <v>282</v>
       </c>
@@ -6366,7 +6392,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="14" t="s">
         <v>283</v>
       </c>
@@ -6384,7 +6410,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="14" t="s">
         <v>285</v>
       </c>
@@ -6402,7 +6428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="14" t="s">
         <v>286</v>
       </c>
@@ -6420,7 +6446,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A245" s="14" t="s">
         <v>287</v>
       </c>
@@ -6492,7 +6518,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="14" t="s">
         <v>291</v>
       </c>
@@ -6510,7 +6536,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A250" s="14" t="s">
         <v>292</v>
       </c>
@@ -6528,7 +6554,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="14" t="s">
         <v>293</v>
       </c>
@@ -6564,7 +6590,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="14" t="s">
         <v>296</v>
       </c>
@@ -6582,7 +6608,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="14" t="s">
         <v>297</v>
       </c>
@@ -6618,7 +6644,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="14" t="s">
         <v>299</v>
       </c>
@@ -6636,7 +6662,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="14" t="s">
         <v>300</v>
       </c>
@@ -6654,7 +6680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" s="14" t="s">
         <v>301</v>
       </c>
@@ -6690,7 +6716,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" s="14" t="s">
         <v>303</v>
       </c>
@@ -6708,7 +6734,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" s="14" t="s">
         <v>304</v>
       </c>
@@ -6726,7 +6752,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" s="14" t="s">
         <v>305</v>
       </c>
@@ -6762,7 +6788,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" s="10" t="s">
         <v>307</v>
       </c>
@@ -6780,7 +6806,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" s="14" t="s">
         <v>308</v>
       </c>
@@ -6798,7 +6824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A266" s="14" t="s">
         <v>309</v>
       </c>
@@ -6816,7 +6842,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A267" s="14" t="s">
         <v>310</v>
       </c>
@@ -6870,7 +6896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" s="14" t="s">
         <v>312</v>
       </c>
@@ -6888,7 +6914,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" s="14" t="s">
         <v>313</v>
       </c>
@@ -6942,7 +6968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" s="14" t="s">
         <v>316</v>
       </c>
@@ -6996,7 +7022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" s="14" t="s">
         <v>319</v>
       </c>
@@ -7014,7 +7040,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" s="14" t="s">
         <v>320</v>
       </c>
@@ -7032,7 +7058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" s="14" t="s">
         <v>321</v>
       </c>
@@ -7050,7 +7076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" s="14" t="s">
         <v>322</v>
       </c>
@@ -7104,7 +7130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" s="14" t="s">
         <v>324</v>
       </c>
@@ -7122,7 +7148,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" s="14" t="s">
         <v>325</v>
       </c>
@@ -7140,7 +7166,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" s="14" t="s">
         <v>326</v>
       </c>
@@ -7158,7 +7184,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" s="14" t="s">
         <v>327</v>
       </c>
@@ -7194,7 +7220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" s="14" t="s">
         <v>329</v>
       </c>
@@ -7212,7 +7238,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" s="14" t="s">
         <v>330</v>
       </c>
@@ -7230,7 +7256,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" s="14" t="s">
         <v>331</v>
       </c>
@@ -7248,7 +7274,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" s="14" t="s">
         <v>332</v>
       </c>
@@ -7266,7 +7292,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" s="14" t="s">
         <v>333</v>
       </c>
@@ -7374,7 +7400,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" s="14" t="s">
         <v>339</v>
       </c>
@@ -7392,7 +7418,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" s="14" t="s">
         <v>340</v>
       </c>
@@ -7410,7 +7436,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" s="14" t="s">
         <v>341</v>
       </c>
@@ -7428,7 +7454,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" s="10" t="s">
         <v>342</v>
       </c>
@@ -7482,7 +7508,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" s="10" t="s">
         <v>346</v>
       </c>
@@ -7500,7 +7526,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" s="10" t="s">
         <v>347</v>
       </c>
@@ -7536,7 +7562,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" s="10" t="s">
         <v>349</v>
       </c>
@@ -7554,7 +7580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A308" s="10" t="s">
         <v>350</v>
       </c>
@@ -7572,7 +7598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="10" t="s">
         <v>351</v>
       </c>
@@ -7608,7 +7634,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="10" t="s">
         <v>353</v>
       </c>
@@ -7626,7 +7652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="10" t="s">
         <v>308</v>
       </c>
@@ -7662,7 +7688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="10" t="s">
         <v>355</v>
       </c>
@@ -8891,7 +8917,7 @@
         <v>10</v>
       </c>
       <c r="C387" s="4" t="str">
-        <f t="shared" ref="C387:C431" si="6">B387</f>
+        <f t="shared" ref="C387:C433" si="6">B387</f>
         <v>Americas</v>
       </c>
       <c r="D387" s="22" t="s">
@@ -9622,6 +9648,42 @@
       </c>
       <c r="E431" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A432" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C432" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Americas</v>
+      </c>
+      <c r="D432" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E432" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A433" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="B433" t="s">
+        <v>6</v>
+      </c>
+      <c r="C433" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>APAC</v>
+      </c>
+      <c r="D433" s="28" t="s">
+        <v>476</v>
+      </c>
+      <c r="E433" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HetalJethva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777E1A11-E2DA-45EE-8DAA-7369ADEADD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18877E2-DDA2-4646-872A-AC2AEC73D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A07144B-59AD-4B98-9627-376AA969DDF8}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="489">
   <si>
     <t>Customer Label</t>
   </si>
@@ -1494,6 +1494,21 @@
   </si>
   <si>
     <t>REHABILITATION DEBTOR MTGOX CO. LTD AND REHABILITATION TRUSTEE AND ATTORNEY</t>
+  </si>
+  <si>
+    <t>Huta Digital OU</t>
+  </si>
+  <si>
+    <t>Dayforce Canada Ltd.</t>
+  </si>
+  <si>
+    <t>Ibtikar Technologies Saudi For Information Technology</t>
+  </si>
+  <si>
+    <t>U FINTECH HUB INC</t>
+  </si>
+  <si>
+    <t>Marek Pasik</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1651,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1708,10 +1723,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2049,7 +2069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0576E467-0835-47AC-A23C-AF9DB748328C}">
-  <dimension ref="A1:E433"/>
+  <dimension ref="A1:E437"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="1"/>
@@ -8917,7 +8937,7 @@
         <v>10</v>
       </c>
       <c r="C387" s="4" t="str">
-        <f t="shared" ref="C387:C433" si="6">B387</f>
+        <f t="shared" ref="C387:C434" si="6">B387</f>
         <v>Americas</v>
       </c>
       <c r="D387" s="22" t="s">
@@ -9684,6 +9704,75 @@
       </c>
       <c r="E433" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>484</v>
+      </c>
+      <c r="B434" t="s">
+        <v>34</v>
+      </c>
+      <c r="C434" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v>MEA</v>
+      </c>
+      <c r="D434" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="E434" s="31" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>485</v>
+      </c>
+      <c r="B435" t="s">
+        <v>10</v>
+      </c>
+      <c r="C435" t="s">
+        <v>10</v>
+      </c>
+      <c r="D435" t="s">
+        <v>17</v>
+      </c>
+      <c r="E435" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>486</v>
+      </c>
+      <c r="B436" t="s">
+        <v>34</v>
+      </c>
+      <c r="C436" t="s">
+        <v>34</v>
+      </c>
+      <c r="D436" t="s">
+        <v>35</v>
+      </c>
+      <c r="E436" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>487</v>
+      </c>
+      <c r="B437" t="s">
+        <v>6</v>
+      </c>
+      <c r="C437" t="s">
+        <v>6</v>
+      </c>
+      <c r="D437" t="s">
+        <v>478</v>
+      </c>
+      <c r="E437" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HetalJethva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://instarempte-my.sharepoint.com/personal/hetal_jethva_nium_com/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18877E2-DDA2-4646-872A-AC2AEC73D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{C18877E2-DDA2-4646-872A-AC2AEC73D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47FC1F49-75A1-42EC-AD42-B59A7ED92C2B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A07144B-59AD-4B98-9627-376AA969DDF8}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$431</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$437</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="485">
   <si>
     <t>Customer Label</t>
   </si>
@@ -281,9 +281,6 @@
     <t>Franklin Technologies ApS</t>
   </si>
   <si>
-    <t>Will Turner</t>
-  </si>
-  <si>
     <t>Gagan Smara</t>
   </si>
   <si>
@@ -698,9 +695,6 @@
     <t>OYSTER HR, INC.</t>
   </si>
   <si>
-    <t>Will turner</t>
-  </si>
-  <si>
     <t>Everpro Holdings Limited</t>
   </si>
   <si>
@@ -896,9 +890,6 @@
     <t>BANCO BS2 S/A</t>
   </si>
   <si>
-    <t>tulio lima</t>
-  </si>
-  <si>
     <t>Banco Ourinvest S.A.</t>
   </si>
   <si>
@@ -1479,9 +1470,6 @@
   </si>
   <si>
     <t>Joon young kim</t>
-  </si>
-  <si>
-    <t>Jerome coelho</t>
   </si>
   <si>
     <t>Irene Tang</t>
@@ -1651,7 +1639,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1683,7 +1671,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1727,11 +1714,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2230,7 +2212,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>23</v>
@@ -2553,7 +2535,7 @@
         <f t="shared" si="0"/>
         <v>EU/UK</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="5" t="s">
@@ -2571,7 +2553,7 @@
         <f t="shared" si="0"/>
         <v>EU/UK</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E28" s="5" t="s">
@@ -2841,7 +2823,7 @@
         <f t="shared" si="0"/>
         <v>Americas</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="11" t="s">
         <v>71</v>
       </c>
       <c r="E43" s="5" t="s">
@@ -2859,7 +2841,7 @@
         <f t="shared" si="0"/>
         <v>APAC</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="12" t="s">
         <v>7</v>
       </c>
       <c r="E44" s="5" t="s">
@@ -2885,7 +2867,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="13" t="s">
         <v>78</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -2896,10 +2878,10 @@
         <v>EU/UK</v>
       </c>
       <c r="D46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -2914,7 +2896,7 @@
         <v>APAC</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>14</v>
@@ -2922,7 +2904,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>6</v>
@@ -2932,7 +2914,7 @@
         <v>APAC</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>14</v>
@@ -2940,7 +2922,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>6</v>
@@ -2958,7 +2940,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>6</v>
@@ -2976,7 +2958,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>20</v>
@@ -2994,7 +2976,7 @@
     </row>
     <row r="52" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>34</v>
@@ -3012,7 +2994,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>25</v>
@@ -3025,12 +3007,12 @@
         <v>11</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>6</v>
@@ -3040,7 +3022,7 @@
         <v>APAC</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>14</v>
@@ -3048,7 +3030,7 @@
     </row>
     <row r="55" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>10</v>
@@ -3065,8 +3047,8 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="14" t="s">
-        <v>91</v>
+      <c r="A56" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>25</v>
@@ -3076,14 +3058,14 @@
         <v>EU/UK</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -3094,15 +3076,15 @@
         <v>EU/UK</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="14" t="s">
-        <v>92</v>
+      <c r="A58" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>25</v>
@@ -3112,15 +3094,15 @@
         <v>EU/UK</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="14" t="s">
-        <v>93</v>
+      <c r="A59" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>25</v>
@@ -3130,7 +3112,7 @@
         <v>EU/UK</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>14</v>
@@ -3138,7 +3120,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>6</v>
@@ -3156,7 +3138,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>20</v>
@@ -3166,7 +3148,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>14</v>
@@ -3191,8 +3173,8 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="14" t="s">
-        <v>97</v>
+      <c r="A63" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>25</v>
@@ -3201,11 +3183,11 @@
         <f t="shared" si="0"/>
         <v>EU/UK</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -3246,7 +3228,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>6</v>
@@ -3264,7 +3246,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>10</v>
@@ -3277,12 +3259,12 @@
         <v>71</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>34</v>
@@ -3300,7 +3282,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>6</v>
@@ -3318,7 +3300,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>6</v>
@@ -3328,7 +3310,7 @@
         <v>APAC</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>14</v>
@@ -3354,7 +3336,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>20</v>
@@ -3364,7 +3346,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>23</v>
@@ -3372,7 +3354,7 @@
     </row>
     <row r="73" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>20</v>
@@ -3385,12 +3367,12 @@
         <v>21</v>
       </c>
       <c r="E73" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="13" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="14" t="s">
-        <v>107</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>25</v>
@@ -3399,16 +3381,16 @@
         <f t="shared" si="1"/>
         <v>EU/UK</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>20</v>
@@ -3462,7 +3444,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>20</v>
@@ -3475,12 +3457,12 @@
         <v>54</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>25</v>
@@ -3489,7 +3471,7 @@
         <f t="shared" si="1"/>
         <v>EU/UK</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E79" s="5" t="s">
@@ -3498,7 +3480,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>10</v>
@@ -3516,7 +3498,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>6</v>
@@ -3534,7 +3516,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>20</v>
@@ -3544,7 +3526,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D82" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>8</v>
@@ -3552,7 +3534,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>25</v>
@@ -3561,7 +3543,7 @@
         <f t="shared" si="1"/>
         <v>EU/UK</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D83" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E83" s="5" t="s">
@@ -3570,7 +3552,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>25</v>
@@ -3579,7 +3561,7 @@
         <f t="shared" si="1"/>
         <v>EU/UK</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E84" s="5" t="s">
@@ -3597,7 +3579,7 @@
         <f t="shared" si="1"/>
         <v>EU/UK</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="D85" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E85" s="5" t="s">
@@ -3606,7 +3588,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>20</v>
@@ -3624,7 +3606,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>20</v>
@@ -3634,7 +3616,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>58</v>
@@ -3642,7 +3624,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>38</v>
@@ -3652,15 +3634,15 @@
         <v>SME</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>10</v>
@@ -3673,7 +3655,7 @@
         <v>17</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
@@ -3687,7 +3669,7 @@
         <f t="shared" si="1"/>
         <v>EU/UK</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E90" s="5" t="s">
@@ -3696,7 +3678,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>6</v>
@@ -3705,8 +3687,8 @@
         <f t="shared" si="1"/>
         <v>APAC</v>
       </c>
-      <c r="D91" s="15" t="s">
-        <v>480</v>
+      <c r="D91" s="14" t="s">
+        <v>476</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>8</v>
@@ -3714,7 +3696,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>6</v>
@@ -3724,15 +3706,15 @@
         <v>APAC</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>25</v>
@@ -3741,7 +3723,7 @@
         <f t="shared" si="1"/>
         <v>EU/UK</v>
       </c>
-      <c r="D93" s="15" t="s">
+      <c r="D93" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E93" s="5" t="s">
@@ -3786,7 +3768,7 @@
     </row>
     <row r="96" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>20</v>
@@ -3796,7 +3778,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>23</v>
@@ -3804,7 +3786,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>10</v>
@@ -3813,16 +3795,16 @@
         <f t="shared" si="1"/>
         <v>Americas</v>
       </c>
-      <c r="D97" s="15" t="s">
+      <c r="D97" s="14" t="s">
         <v>11</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>6</v>
@@ -3831,7 +3813,7 @@
         <f t="shared" si="1"/>
         <v>APAC</v>
       </c>
-      <c r="D98" s="15" t="s">
+      <c r="D98" s="14" t="s">
         <v>67</v>
       </c>
       <c r="E98" s="5" t="s">
@@ -3840,7 +3822,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>10</v>
@@ -3868,7 +3850,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>23</v>
@@ -3876,7 +3858,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>10</v>
@@ -3889,12 +3871,12 @@
         <v>17</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>6</v>
@@ -3912,7 +3894,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>10</v>
@@ -3925,12 +3907,12 @@
         <v>17</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>6</v>
@@ -3948,7 +3930,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>25</v>
@@ -3966,7 +3948,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>10</v>
@@ -3979,12 +3961,12 @@
         <v>71</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>34</v>
@@ -4002,7 +3984,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>6</v>
@@ -4020,7 +4002,7 @@
     </row>
     <row r="109" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>6</v>
@@ -4038,7 +4020,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>34</v>
@@ -4056,7 +4038,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>20</v>
@@ -4074,7 +4056,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>20</v>
@@ -4092,7 +4074,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>6</v>
@@ -4102,7 +4084,7 @@
         <v>APAC</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>63</v>
@@ -4110,7 +4092,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>20</v>
@@ -4128,7 +4110,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>10</v>
@@ -4137,7 +4119,7 @@
         <f t="shared" si="1"/>
         <v>Americas</v>
       </c>
-      <c r="D115" s="16" t="s">
+      <c r="D115" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E115" s="5" t="s">
@@ -4146,7 +4128,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>10</v>
@@ -4159,12 +4141,12 @@
         <v>11</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>10</v>
@@ -4182,7 +4164,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>10</v>
@@ -4200,7 +4182,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>25</v>
@@ -4218,7 +4200,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>10</v>
@@ -4236,7 +4218,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B121" s="8" t="s">
         <v>25</v>
@@ -4245,7 +4227,7 @@
         <f t="shared" si="1"/>
         <v>EU/UK</v>
       </c>
-      <c r="D121" s="5" t="s">
+      <c r="D121" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E121" s="5" t="s">
@@ -4254,7 +4236,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>10</v>
@@ -4272,7 +4254,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>10</v>
@@ -4290,7 +4272,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>6</v>
@@ -4308,7 +4290,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>6</v>
@@ -4326,7 +4308,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>20</v>
@@ -4344,7 +4326,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>34</v>
@@ -4362,7 +4344,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>6</v>
@@ -4371,8 +4353,8 @@
         <f t="shared" si="1"/>
         <v>APAC</v>
       </c>
-      <c r="D128" s="13" t="s">
-        <v>81</v>
+      <c r="D128" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="E128" s="5" t="s">
         <v>8</v>
@@ -4380,7 +4362,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>25</v>
@@ -4390,15 +4372,15 @@
         <v>EU/UK</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>6</v>
@@ -4407,8 +4389,8 @@
         <f t="shared" si="1"/>
         <v>APAC</v>
       </c>
-      <c r="D130" s="13" t="s">
-        <v>81</v>
+      <c r="D130" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>8</v>
@@ -4416,7 +4398,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>20</v>
@@ -4426,7 +4408,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>23</v>
@@ -4434,7 +4416,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>6</v>
@@ -4452,7 +4434,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>20</v>
@@ -4462,7 +4444,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>8</v>
@@ -4470,7 +4452,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>20</v>
@@ -4483,12 +4465,12 @@
         <v>54</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>20</v>
@@ -4498,7 +4480,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>8</v>
@@ -4506,7 +4488,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>20</v>
@@ -4519,12 +4501,12 @@
         <v>32</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>20</v>
@@ -4534,7 +4516,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>8</v>
@@ -4542,7 +4524,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>20</v>
@@ -4552,15 +4534,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>20</v>
@@ -4570,15 +4552,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>6</v>
@@ -4587,16 +4569,16 @@
         <f t="shared" si="2"/>
         <v>APAC</v>
       </c>
-      <c r="D140" s="15" t="s">
+      <c r="D140" s="14" t="s">
         <v>7</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>20</v>
@@ -4614,7 +4596,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>6</v>
@@ -4632,7 +4614,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>6</v>
@@ -4642,7 +4624,7 @@
         <v>APAC</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>8</v>
@@ -4650,7 +4632,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>10</v>
@@ -4668,7 +4650,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>20</v>
@@ -4678,15 +4660,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>10</v>
@@ -4704,7 +4686,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>10</v>
@@ -4714,15 +4696,15 @@
         <v>Americas</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>10</v>
@@ -4732,7 +4714,7 @@
         <v>Americas</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>58</v>
@@ -4740,7 +4722,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>10</v>
@@ -4750,7 +4732,7 @@
         <v>Americas</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>58</v>
@@ -4758,7 +4740,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>6</v>
@@ -4768,7 +4750,7 @@
         <v>APAC</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>23</v>
@@ -4776,7 +4758,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>10</v>
@@ -4786,15 +4768,15 @@
         <v>Americas</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>6</v>
@@ -4804,7 +4786,7 @@
         <v>APAC</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E152" s="5" t="s">
         <v>8</v>
@@ -4812,7 +4794,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>10</v>
@@ -4822,7 +4804,7 @@
         <v>Americas</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E153" s="5" t="s">
         <v>8</v>
@@ -4830,7 +4812,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>10</v>
@@ -4840,7 +4822,7 @@
         <v>Americas</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>58</v>
@@ -4848,7 +4830,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>6</v>
@@ -4858,7 +4840,7 @@
         <v>APAC</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E155" s="5" t="s">
         <v>36</v>
@@ -4866,7 +4848,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>10</v>
@@ -4876,7 +4858,7 @@
         <v>Americas</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E156" s="5" t="s">
         <v>58</v>
@@ -4884,7 +4866,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>6</v>
@@ -4894,15 +4876,15 @@
         <v>APAC</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>6</v>
@@ -4912,15 +4894,15 @@
         <v>APAC</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>20</v>
@@ -4933,12 +4915,12 @@
         <v>32</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>10</v>
@@ -4948,15 +4930,15 @@
         <v>Americas</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>6</v>
@@ -4969,12 +4951,12 @@
         <v>30</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A162" s="25" t="s">
-        <v>199</v>
+      <c r="A162" s="24" t="s">
+        <v>198</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>10</v>
@@ -4984,15 +4966,15 @@
         <v>Americas</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A163" s="17" t="s">
-        <v>200</v>
+      <c r="A163" s="16" t="s">
+        <v>199</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>10</v>
@@ -5001,16 +4983,16 @@
         <f t="shared" si="2"/>
         <v>Americas</v>
       </c>
-      <c r="D163" s="15" t="s">
+      <c r="D163" s="14" t="s">
         <v>11</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A164" s="25" t="s">
-        <v>201</v>
+      <c r="A164" s="24" t="s">
+        <v>200</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>10</v>
@@ -5020,15 +5002,15 @@
         <v>Americas</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A165" s="17" t="s">
-        <v>202</v>
+      <c r="A165" s="16" t="s">
+        <v>201</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>10</v>
@@ -5038,15 +5020,15 @@
         <v>Americas</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E165" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A166" s="16" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A166" s="17" t="s">
-        <v>204</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>20</v>
@@ -5063,8 +5045,8 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A167" s="17" t="s">
-        <v>205</v>
+      <c r="A167" s="16" t="s">
+        <v>204</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>20</v>
@@ -5077,12 +5059,12 @@
         <v>54</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A168" s="17" t="s">
-        <v>206</v>
+      <c r="A168" s="16" t="s">
+        <v>205</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>20</v>
@@ -5092,15 +5074,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A169" s="25" t="s">
-        <v>207</v>
+      <c r="A169" s="24" t="s">
+        <v>206</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>10</v>
@@ -5110,7 +5092,7 @@
         <v>Americas</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E169" s="5" t="s">
         <v>58</v>
@@ -5118,7 +5100,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>6</v>
@@ -5128,7 +5110,7 @@
         <v>APAC</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E170" s="5" t="s">
         <v>14</v>
@@ -5136,7 +5118,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
@@ -5154,7 +5136,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>6</v>
@@ -5172,7 +5154,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>20</v>
@@ -5190,7 +5172,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>10</v>
@@ -5199,7 +5181,7 @@
         <f t="shared" si="2"/>
         <v>Americas</v>
       </c>
-      <c r="D174" s="15" t="s">
+      <c r="D174" s="14" t="s">
         <v>11</v>
       </c>
       <c r="E174" s="5" t="s">
@@ -5208,7 +5190,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>25</v>
@@ -5226,7 +5208,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>25</v>
@@ -5244,7 +5226,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>6</v>
@@ -5254,7 +5236,7 @@
         <v>APAC</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E177" s="5" t="s">
         <v>8</v>
@@ -5262,7 +5244,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>20</v>
@@ -5280,7 +5262,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>25</v>
@@ -5289,8 +5271,8 @@
         <f t="shared" si="2"/>
         <v>EU/UK</v>
       </c>
-      <c r="D179" s="5" t="s">
-        <v>218</v>
+      <c r="D179" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="E179" s="5" t="s">
         <v>8</v>
@@ -5298,7 +5280,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>20</v>
@@ -5308,7 +5290,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E180" s="5" t="s">
         <v>63</v>
@@ -5316,7 +5298,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>34</v>
@@ -5329,12 +5311,12 @@
         <v>35</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>20</v>
@@ -5352,7 +5334,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>34</v>
@@ -5370,7 +5352,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>20</v>
@@ -5383,12 +5365,12 @@
         <v>32</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>20</v>
@@ -5398,15 +5380,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>34</v>
@@ -5424,7 +5406,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>10</v>
@@ -5442,7 +5424,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>10</v>
@@ -5455,12 +5437,12 @@
         <v>71</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>20</v>
@@ -5478,7 +5460,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>10</v>
@@ -5491,12 +5473,12 @@
         <v>17</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>10</v>
@@ -5509,12 +5491,12 @@
         <v>17</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>10</v>
@@ -5527,12 +5509,12 @@
         <v>17</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>6</v>
@@ -5542,15 +5524,15 @@
         <v>APAC</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>6</v>
@@ -5560,7 +5542,7 @@
         <v>APAC</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E194" s="5" t="s">
         <v>8</v>
@@ -5568,7 +5550,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>25</v>
@@ -5586,7 +5568,7 @@
     </row>
     <row r="196" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>6</v>
@@ -5604,7 +5586,7 @@
     </row>
     <row r="197" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>6</v>
@@ -5622,7 +5604,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>20</v>
@@ -5640,7 +5622,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>20</v>
@@ -5653,12 +5635,12 @@
         <v>54</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>20</v>
@@ -5671,12 +5653,12 @@
         <v>21</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>10</v>
@@ -5686,7 +5668,7 @@
         <v>Americas</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>8</v>
@@ -5694,7 +5676,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>20</v>
@@ -5704,15 +5686,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>10</v>
@@ -5722,7 +5704,7 @@
         <v>Americas</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E203" s="5" t="s">
         <v>8</v>
@@ -5730,7 +5712,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>20</v>
@@ -5740,15 +5722,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E204" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A205" s="14" t="s">
-        <v>246</v>
+      <c r="A205" s="13" t="s">
+        <v>244</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>25</v>
@@ -5757,16 +5739,16 @@
         <f t="shared" si="3"/>
         <v>EU/UK</v>
       </c>
-      <c r="D205" s="11" t="s">
+      <c r="D205" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>6</v>
@@ -5776,15 +5758,15 @@
         <v>APAC</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E206" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>10</v>
@@ -5802,7 +5784,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>20</v>
@@ -5820,7 +5802,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>20</v>
@@ -5838,7 +5820,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>25</v>
@@ -5848,7 +5830,7 @@
         <v>EU/UK</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E210" s="5" t="s">
         <v>8</v>
@@ -5856,7 +5838,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>10</v>
@@ -5869,12 +5851,12 @@
         <v>11</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>20</v>
@@ -5892,7 +5874,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>6</v>
@@ -5902,7 +5884,7 @@
         <v>APAC</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E213" s="5" t="s">
         <v>23</v>
@@ -5910,7 +5892,7 @@
     </row>
     <row r="214" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A214" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B214" s="4" t="s">
         <v>6</v>
@@ -5920,15 +5902,15 @@
         <v>APAC</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>6</v>
@@ -5946,7 +5928,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>20</v>
@@ -5964,7 +5946,7 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>34</v>
@@ -5977,12 +5959,12 @@
         <v>35</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>10</v>
@@ -5995,12 +5977,12 @@
         <v>11</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>6</v>
@@ -6010,7 +5992,7 @@
         <v>APAC</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>14</v>
@@ -6018,7 +6000,7 @@
     </row>
     <row r="220" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A220" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>20</v>
@@ -6028,15 +6010,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>20</v>
@@ -6045,16 +6027,16 @@
         <f t="shared" si="3"/>
         <v>Shared Center</v>
       </c>
-      <c r="D221" s="18" t="s">
+      <c r="D221" s="17" t="s">
         <v>21</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>34</v>
@@ -6072,7 +6054,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>6</v>
@@ -6082,7 +6064,7 @@
         <v>APAC</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E223" s="5" t="s">
         <v>8</v>
@@ -6090,7 +6072,7 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>6</v>
@@ -6100,7 +6082,7 @@
         <v>APAC</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E224" s="5" t="s">
         <v>8</v>
@@ -6108,7 +6090,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>6</v>
@@ -6118,7 +6100,7 @@
         <v>APAC</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E225" s="5" t="s">
         <v>8</v>
@@ -6126,7 +6108,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B226" s="4" t="s">
         <v>6</v>
@@ -6135,8 +6117,8 @@
         <f t="shared" si="3"/>
         <v>APAC</v>
       </c>
-      <c r="D226" s="19" t="s">
-        <v>81</v>
+      <c r="D226" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="E226" s="5" t="s">
         <v>8</v>
@@ -6144,7 +6126,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>34</v>
@@ -6162,7 +6144,7 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>34</v>
@@ -6180,7 +6162,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>34</v>
@@ -6198,7 +6180,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B230" s="4" t="s">
         <v>10</v>
@@ -6216,7 +6198,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>20</v>
@@ -6234,7 +6216,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>20</v>
@@ -6247,12 +6229,12 @@
         <v>21</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>6</v>
@@ -6270,7 +6252,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B234" s="4" t="s">
         <v>6</v>
@@ -6280,7 +6262,7 @@
         <v>APAC</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E234" s="5" t="s">
         <v>63</v>
@@ -6288,7 +6270,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>20</v>
@@ -6306,7 +6288,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>20</v>
@@ -6316,15 +6298,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>20</v>
@@ -6341,8 +6323,8 @@
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A238" s="14" t="s">
-        <v>279</v>
+      <c r="A238" s="13" t="s">
+        <v>277</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>34</v>
@@ -6359,10 +6341,10 @@
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A239" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="B239" s="20" t="s">
+      <c r="A239" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B239" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C239" s="4" t="str">
@@ -6370,15 +6352,15 @@
         <v>APAC</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E239" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A240" s="14" t="s">
-        <v>281</v>
+      <c r="A240" s="13" t="s">
+        <v>279</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>34</v>
@@ -6395,8 +6377,8 @@
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A241" s="14" t="s">
-        <v>282</v>
+      <c r="A241" s="13" t="s">
+        <v>280</v>
       </c>
       <c r="B241" s="4" t="s">
         <v>10</v>
@@ -6409,12 +6391,12 @@
         <v>11</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A242" s="14" t="s">
-        <v>283</v>
+      <c r="A242" s="13" t="s">
+        <v>281</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>10</v>
@@ -6423,16 +6405,16 @@
         <f t="shared" si="3"/>
         <v>Americas</v>
       </c>
-      <c r="D242" s="11" t="s">
-        <v>284</v>
+      <c r="D242" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A243" s="14" t="s">
-        <v>285</v>
+      <c r="A243" s="13" t="s">
+        <v>282</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>10</v>
@@ -6442,15 +6424,15 @@
         <v>Americas</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A244" s="14" t="s">
-        <v>286</v>
+      <c r="A244" s="13" t="s">
+        <v>283</v>
       </c>
       <c r="B244" s="4" t="s">
         <v>20</v>
@@ -6463,12 +6445,12 @@
         <v>32</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="245" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A245" s="14" t="s">
-        <v>287</v>
+      <c r="A245" s="13" t="s">
+        <v>284</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>20</v>
@@ -6478,17 +6460,17 @@
         <v>Shared Center</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="B246" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="B246" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C246" s="4" t="str">
@@ -6496,15 +6478,15 @@
         <v>APAC</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A247" s="14" t="s">
-        <v>289</v>
+      <c r="A247" s="13" t="s">
+        <v>286</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>20</v>
@@ -6514,7 +6496,7 @@
         <v>Shared Center</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E247" s="6" t="s">
         <v>8</v>
@@ -6522,9 +6504,9 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B248" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="B248" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C248" s="4" t="str">
@@ -6532,15 +6514,15 @@
         <v>APAC</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A249" s="14" t="s">
-        <v>291</v>
+      <c r="A249" s="13" t="s">
+        <v>288</v>
       </c>
       <c r="B249" s="4" t="s">
         <v>34</v>
@@ -6557,10 +6539,10 @@
       </c>
     </row>
     <row r="250" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A250" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B250" s="20" t="s">
+      <c r="A250" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="B250" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C250" s="4" t="str">
@@ -6568,15 +6550,15 @@
         <v>APAC</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A251" s="14" t="s">
-        <v>293</v>
+      <c r="A251" s="13" t="s">
+        <v>290</v>
       </c>
       <c r="B251" s="4" t="s">
         <v>34</v>
@@ -6594,9 +6576,9 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="B252" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="B252" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C252" s="4" t="str">
@@ -6604,17 +6586,17 @@
         <v>APAC</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A253" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="B253" s="20" t="s">
+      <c r="A253" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="B253" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C253" s="4" t="str">
@@ -6622,17 +6604,17 @@
         <v>APAC</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E253" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A254" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="B254" s="20" t="s">
+      <c r="A254" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B254" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C254" s="4" t="str">
@@ -6640,17 +6622,17 @@
         <v>APAC</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E254" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="B255" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="B255" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C255" s="4" t="str">
@@ -6658,15 +6640,15 @@
         <v>APAC</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E255" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A256" s="14" t="s">
-        <v>299</v>
+      <c r="A256" s="13" t="s">
+        <v>296</v>
       </c>
       <c r="B256" s="8" t="s">
         <v>25</v>
@@ -6676,15 +6658,15 @@
         <v>EU/UK</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A257" s="14" t="s">
-        <v>300</v>
+      <c r="A257" s="13" t="s">
+        <v>297</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>20</v>
@@ -6701,8 +6683,8 @@
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A258" s="14" t="s">
-        <v>301</v>
+      <c r="A258" s="13" t="s">
+        <v>298</v>
       </c>
       <c r="B258" s="4" t="s">
         <v>10</v>
@@ -6711,8 +6693,8 @@
         <f t="shared" si="3"/>
         <v>Americas</v>
       </c>
-      <c r="D258" s="6" t="s">
-        <v>190</v>
+      <c r="D258" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>8</v>
@@ -6720,7 +6702,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B259" s="4" t="s">
         <v>10</v>
@@ -6730,17 +6712,17 @@
         <v>Americas</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E259" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A260" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="B260" s="20" t="s">
+      <c r="A260" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="B260" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C260" s="4" t="str">
@@ -6755,8 +6737,8 @@
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A261" s="14" t="s">
-        <v>304</v>
+      <c r="A261" s="13" t="s">
+        <v>301</v>
       </c>
       <c r="B261" s="4" t="s">
         <v>20</v>
@@ -6773,8 +6755,8 @@
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A262" s="14" t="s">
-        <v>305</v>
+      <c r="A262" s="13" t="s">
+        <v>302</v>
       </c>
       <c r="B262" s="4" t="s">
         <v>34</v>
@@ -6792,9 +6774,9 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="B263" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B263" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C263" s="4" t="str">
@@ -6802,7 +6784,7 @@
         <v>APAC</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E263" s="6" t="s">
         <v>63</v>
@@ -6810,7 +6792,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B264" s="4" t="s">
         <v>6</v>
@@ -6827,8 +6809,8 @@
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A265" s="14" t="s">
-        <v>308</v>
+      <c r="A265" s="13" t="s">
+        <v>305</v>
       </c>
       <c r="B265" s="4" t="s">
         <v>20</v>
@@ -6845,8 +6827,8 @@
       </c>
     </row>
     <row r="266" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A266" s="14" t="s">
-        <v>309</v>
+      <c r="A266" s="13" t="s">
+        <v>306</v>
       </c>
       <c r="B266" s="4" t="s">
         <v>34</v>
@@ -6863,8 +6845,8 @@
       </c>
     </row>
     <row r="267" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A267" s="14" t="s">
-        <v>310</v>
+      <c r="A267" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="B267" s="4" t="s">
         <v>34</v>
@@ -6882,9 +6864,9 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B268" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="B268" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C268" s="4" t="str">
@@ -6892,7 +6874,7 @@
         <v>SME</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>8</v>
@@ -6900,9 +6882,9 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B269" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="B269" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C269" s="4" t="str">
@@ -6910,15 +6892,15 @@
         <v>SME</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E269" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A270" s="14" t="s">
-        <v>312</v>
+      <c r="A270" s="13" t="s">
+        <v>309</v>
       </c>
       <c r="B270" s="4" t="s">
         <v>20</v>
@@ -6935,8 +6917,8 @@
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A271" s="14" t="s">
-        <v>313</v>
+      <c r="A271" s="13" t="s">
+        <v>310</v>
       </c>
       <c r="B271" s="4" t="s">
         <v>20</v>
@@ -6953,8 +6935,8 @@
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A272" s="14" t="s">
-        <v>314</v>
+      <c r="A272" s="13" t="s">
+        <v>311</v>
       </c>
       <c r="B272" s="4" t="s">
         <v>10</v>
@@ -6963,16 +6945,16 @@
         <f t="shared" si="4"/>
         <v>Americas</v>
       </c>
-      <c r="D272" s="6" t="s">
-        <v>190</v>
+      <c r="D272" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A273" s="14" t="s">
-        <v>315</v>
+      <c r="A273" s="13" t="s">
+        <v>312</v>
       </c>
       <c r="B273" s="4" t="s">
         <v>34</v>
@@ -6982,15 +6964,15 @@
         <v>MEA</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E273" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A274" s="14" t="s">
-        <v>316</v>
+      <c r="A274" s="13" t="s">
+        <v>313</v>
       </c>
       <c r="B274" s="4" t="s">
         <v>34</v>
@@ -7007,10 +6989,10 @@
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A275" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="B275" s="20" t="s">
+      <c r="A275" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="B275" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C275" s="4" t="str">
@@ -7025,10 +7007,10 @@
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A276" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="B276" s="20" t="s">
+      <c r="A276" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B276" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C276" s="4" t="str">
@@ -7043,8 +7025,8 @@
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A277" s="14" t="s">
-        <v>319</v>
+      <c r="A277" s="13" t="s">
+        <v>316</v>
       </c>
       <c r="B277" s="4" t="s">
         <v>10</v>
@@ -7053,16 +7035,16 @@
         <f t="shared" si="4"/>
         <v>Americas</v>
       </c>
-      <c r="D277" s="6" t="s">
-        <v>190</v>
+      <c r="D277" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E277" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A278" s="14" t="s">
-        <v>320</v>
+      <c r="A278" s="13" t="s">
+        <v>317</v>
       </c>
       <c r="B278" s="4" t="s">
         <v>20</v>
@@ -7079,8 +7061,8 @@
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A279" s="14" t="s">
-        <v>321</v>
+      <c r="A279" s="13" t="s">
+        <v>318</v>
       </c>
       <c r="B279" s="4" t="s">
         <v>20</v>
@@ -7090,15 +7072,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E279" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A280" s="14" t="s">
-        <v>322</v>
+      <c r="A280" s="13" t="s">
+        <v>319</v>
       </c>
       <c r="B280" s="4" t="s">
         <v>20</v>
@@ -7108,17 +7090,17 @@
         <v>Shared Center</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A281" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="B281" s="20" t="s">
+      <c r="A281" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B281" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C281" s="4" t="str">
@@ -7126,17 +7108,17 @@
         <v>APAC</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E281" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A282" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="B282" s="20" t="s">
+      <c r="A282" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B282" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C282" s="4" t="str">
@@ -7144,15 +7126,15 @@
         <v>APAC</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E282" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A283" s="14" t="s">
-        <v>324</v>
+      <c r="A283" s="13" t="s">
+        <v>321</v>
       </c>
       <c r="B283" s="4" t="s">
         <v>34</v>
@@ -7169,8 +7151,8 @@
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A284" s="14" t="s">
-        <v>325</v>
+      <c r="A284" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="B284" s="4" t="s">
         <v>20</v>
@@ -7187,8 +7169,8 @@
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A285" s="14" t="s">
-        <v>326</v>
+      <c r="A285" s="13" t="s">
+        <v>323</v>
       </c>
       <c r="B285" s="4" t="s">
         <v>10</v>
@@ -7197,18 +7179,18 @@
         <f t="shared" si="4"/>
         <v>Americas</v>
       </c>
-      <c r="D285" s="6" t="s">
-        <v>190</v>
+      <c r="D285" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E285" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A286" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="B286" s="20" t="s">
+      <c r="A286" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="B286" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C286" s="4" t="str">
@@ -7216,17 +7198,17 @@
         <v>APAC</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E286" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B287" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B287" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C287" s="4" t="str">
@@ -7234,15 +7216,15 @@
         <v>APAC</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E287" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A288" s="14" t="s">
-        <v>329</v>
+      <c r="A288" s="13" t="s">
+        <v>326</v>
       </c>
       <c r="B288" s="4" t="s">
         <v>10</v>
@@ -7251,16 +7233,16 @@
         <f t="shared" si="4"/>
         <v>Americas</v>
       </c>
-      <c r="D288" s="6" t="s">
-        <v>190</v>
+      <c r="D288" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E288" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A289" s="14" t="s">
-        <v>330</v>
+      <c r="A289" s="13" t="s">
+        <v>327</v>
       </c>
       <c r="B289" s="4" t="s">
         <v>20</v>
@@ -7277,8 +7259,8 @@
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A290" s="14" t="s">
-        <v>331</v>
+      <c r="A290" s="13" t="s">
+        <v>328</v>
       </c>
       <c r="B290" s="4" t="s">
         <v>20</v>
@@ -7295,8 +7277,8 @@
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A291" s="14" t="s">
-        <v>332</v>
+      <c r="A291" s="13" t="s">
+        <v>329</v>
       </c>
       <c r="B291" s="4" t="s">
         <v>20</v>
@@ -7306,15 +7288,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E291" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A292" s="14" t="s">
-        <v>333</v>
+      <c r="A292" s="13" t="s">
+        <v>330</v>
       </c>
       <c r="B292" s="4" t="s">
         <v>34</v>
@@ -7331,8 +7313,8 @@
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A293" s="14" t="s">
-        <v>334</v>
+      <c r="A293" s="13" t="s">
+        <v>331</v>
       </c>
       <c r="B293" s="4" t="s">
         <v>10</v>
@@ -7350,9 +7332,9 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B294" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B294" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C294" s="4" t="str">
@@ -7360,7 +7342,7 @@
         <v>APAC</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E294" s="6" t="s">
         <v>63</v>
@@ -7368,7 +7350,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B295" s="4" t="s">
         <v>10</v>
@@ -7378,7 +7360,7 @@
         <v>Americas</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E295" s="6" t="s">
         <v>58</v>
@@ -7386,9 +7368,9 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B296" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B296" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C296" s="4" t="str">
@@ -7396,17 +7378,17 @@
         <v>APAC</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E296" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="B297" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="B297" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C297" s="4" t="str">
@@ -7414,15 +7396,15 @@
         <v>APAC</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E297" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A298" s="14" t="s">
-        <v>339</v>
+      <c r="A298" s="13" t="s">
+        <v>336</v>
       </c>
       <c r="B298" s="4" t="s">
         <v>34</v>
@@ -7439,8 +7421,8 @@
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A299" s="14" t="s">
-        <v>340</v>
+      <c r="A299" s="13" t="s">
+        <v>337</v>
       </c>
       <c r="B299" s="4" t="s">
         <v>20</v>
@@ -7450,15 +7432,15 @@
         <v>Shared Center</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E299" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A300" s="14" t="s">
-        <v>341</v>
+      <c r="A300" s="13" t="s">
+        <v>338</v>
       </c>
       <c r="B300" s="4" t="s">
         <v>10</v>
@@ -7467,8 +7449,8 @@
         <f t="shared" si="4"/>
         <v>Americas</v>
       </c>
-      <c r="D300" s="6" t="s">
-        <v>190</v>
+      <c r="D300" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E300" s="6" t="s">
         <v>58</v>
@@ -7476,7 +7458,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" s="10" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B301" s="4" t="s">
         <v>20</v>
@@ -7489,14 +7471,14 @@
         <v>32</v>
       </c>
       <c r="E301" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B302" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="B302" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C302" s="4" t="str">
@@ -7504,17 +7486,17 @@
         <v>APAC</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E302" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="B303" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="B303" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C303" s="4" t="str">
@@ -7522,15 +7504,15 @@
         <v>APAC</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E303" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" s="10" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B304" s="4" t="s">
         <v>10</v>
@@ -7548,7 +7530,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" s="10" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B305" s="4" t="s">
         <v>10</v>
@@ -7566,7 +7548,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B306" s="4" t="s">
         <v>10</v>
@@ -7576,7 +7558,7 @@
         <v>Americas</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E306" s="6" t="s">
         <v>58</v>
@@ -7584,9 +7566,9 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="B307" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="B307" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C307" s="4" t="str">
@@ -7602,7 +7584,7 @@
     </row>
     <row r="308" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A308" s="10" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B308" s="4" t="s">
         <v>20</v>
@@ -7620,7 +7602,7 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="10" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B309" s="4" t="s">
         <v>34</v>
@@ -7629,7 +7611,7 @@
         <f t="shared" si="4"/>
         <v>MEA</v>
       </c>
-      <c r="D309" s="6" t="s">
+      <c r="D309" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E309" s="6" t="s">
@@ -7638,7 +7620,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B310" s="4" t="s">
         <v>20</v>
@@ -7656,7 +7638,7 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="10" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B311" s="4" t="s">
         <v>20</v>
@@ -7674,7 +7656,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>20</v>
@@ -7692,7 +7674,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B313" s="4" t="s">
         <v>20</v>
@@ -7710,7 +7692,7 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="10" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B314" s="4" t="s">
         <v>20</v>
@@ -7728,7 +7710,7 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B315" s="4" t="s">
         <v>34</v>
@@ -7738,7 +7720,7 @@
         <v>MEA</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E315" s="6" t="s">
         <v>73</v>
@@ -7746,7 +7728,7 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B316" s="4" t="s">
         <v>10</v>
@@ -7756,7 +7738,7 @@
         <v>Americas</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E316" s="6" t="s">
         <v>58</v>
@@ -7764,7 +7746,7 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B317" s="4" t="s">
         <v>34</v>
@@ -7774,7 +7756,7 @@
         <v>MEA</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E317" s="6" t="s">
         <v>73</v>
@@ -7782,9 +7764,9 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="B318" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="B318" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C318" s="4" t="str">
@@ -7792,17 +7774,17 @@
         <v>APAC</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E318" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A319" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="B319" s="20" t="s">
+      <c r="A319" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B319" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C319" s="4" t="str">
@@ -7810,7 +7792,7 @@
         <v>APAC</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E319" s="6" t="s">
         <v>63</v>
@@ -7818,7 +7800,7 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B320" s="8" t="s">
         <v>25</v>
@@ -7828,15 +7810,15 @@
         <v>EU/UK</v>
       </c>
       <c r="D320" s="6" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E320" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A321" s="21" t="s">
-        <v>362</v>
+      <c r="A321" s="20" t="s">
+        <v>359</v>
       </c>
       <c r="B321" s="4" t="s">
         <v>10</v>
@@ -7846,7 +7828,7 @@
         <v>Americas</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E321" s="6" t="s">
         <v>58</v>
@@ -7854,7 +7836,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B322" s="4" t="s">
         <v>20</v>
@@ -7872,7 +7854,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B323" s="4" t="s">
         <v>20</v>
@@ -7890,7 +7872,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B324" s="4" t="s">
         <v>10</v>
@@ -7908,9 +7890,9 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="B325" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="B325" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C325" s="4" t="str">
@@ -7918,15 +7900,15 @@
         <v>EU/UK</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E325" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B326" s="4" t="s">
         <v>10</v>
@@ -7936,7 +7918,7 @@
         <v>Americas</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E326" s="6" t="s">
         <v>58</v>
@@ -7944,7 +7926,7 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B327" s="4" t="s">
         <v>34</v>
@@ -7954,7 +7936,7 @@
         <v>MEA</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E327" s="6" t="s">
         <v>73</v>
@@ -7962,7 +7944,7 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B328" s="4" t="s">
         <v>34</v>
@@ -7972,7 +7954,7 @@
         <v>MEA</v>
       </c>
       <c r="D328" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E328" s="6" t="s">
         <v>73</v>
@@ -7980,9 +7962,9 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="B329" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="B329" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C329" s="4" t="str">
@@ -7990,15 +7972,15 @@
         <v>APAC</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E329" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B330" s="4" t="s">
         <v>10</v>
@@ -8008,7 +7990,7 @@
         <v>Americas</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E330" s="6" t="s">
         <v>58</v>
@@ -8016,7 +7998,7 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B331" s="4" t="s">
         <v>34</v>
@@ -8025,7 +8007,7 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D331" s="6" t="s">
+      <c r="D331" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E331" s="6" t="s">
@@ -8034,7 +8016,7 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B332" s="4" t="s">
         <v>20</v>
@@ -8047,12 +8029,12 @@
         <v>21</v>
       </c>
       <c r="E332" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B333" s="4" t="s">
         <v>20</v>
@@ -8070,7 +8052,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B334" s="4" t="s">
         <v>34</v>
@@ -8079,7 +8061,7 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D334" s="6" t="s">
+      <c r="D334" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E334" s="6" t="s">
@@ -8088,7 +8070,7 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B335" s="4" t="s">
         <v>10</v>
@@ -8106,9 +8088,9 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="B336" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="B336" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C336" s="4" t="str">
@@ -8116,17 +8098,17 @@
         <v>EU/UK</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E336" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="B337" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="B337" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C337" s="4" t="str">
@@ -8134,17 +8116,17 @@
         <v>APAC</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E337" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="B338" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="B338" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C338" s="4" t="str">
@@ -8152,15 +8134,15 @@
         <v>APAC</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E338" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="6" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B339" s="4" t="s">
         <v>10</v>
@@ -8178,7 +8160,7 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B340" s="4" t="s">
         <v>10</v>
@@ -8188,17 +8170,17 @@
         <v>Americas</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E340" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="B341" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="B341" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C341" s="4" t="str">
@@ -8214,7 +8196,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B342" s="4" t="s">
         <v>25</v>
@@ -8232,7 +8214,7 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B343" s="4" t="s">
         <v>25</v>
@@ -8250,7 +8232,7 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B344" t="s">
         <v>6</v>
@@ -8262,13 +8244,13 @@
       <c r="D344" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E344" s="23" t="s">
+      <c r="E344" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B345" t="s">
         <v>6</v>
@@ -8277,13 +8259,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D345" s="22" t="s">
-        <v>81</v>
+      <c r="D345" s="21" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B346" t="s">
         <v>38</v>
@@ -8292,13 +8274,13 @@
         <f t="shared" si="5"/>
         <v>SME</v>
       </c>
-      <c r="D346" s="22" t="s">
-        <v>476</v>
+      <c r="D346" s="21" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B347" t="s">
         <v>34</v>
@@ -8307,16 +8289,16 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D347" s="22" t="s">
+      <c r="D347" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E347" s="23" t="s">
+      <c r="E347" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B348" t="s">
         <v>10</v>
@@ -8325,13 +8307,13 @@
         <f t="shared" si="5"/>
         <v>Americas</v>
       </c>
-      <c r="D348" s="22" t="s">
-        <v>190</v>
+      <c r="D348" s="5" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B349" t="s">
         <v>6</v>
@@ -8340,13 +8322,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D349" s="22" t="s">
-        <v>81</v>
+      <c r="D349" s="21" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B350" t="s">
         <v>20</v>
@@ -8361,7 +8343,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B351" t="s">
         <v>20</v>
@@ -8370,13 +8352,13 @@
         <f t="shared" si="5"/>
         <v>Shared Center</v>
       </c>
-      <c r="D351" s="18" t="s">
+      <c r="D351" s="17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B352" t="s">
         <v>20</v>
@@ -8386,12 +8368,12 @@
         <v>Shared Center</v>
       </c>
       <c r="D352" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B353" s="4" t="s">
         <v>25</v>
@@ -8406,7 +8388,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B354" t="s">
         <v>6</v>
@@ -8415,13 +8397,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D354" s="22" t="s">
-        <v>81</v>
+      <c r="D354" s="21" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B355" t="s">
         <v>20</v>
@@ -8436,7 +8418,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B356" t="s">
         <v>34</v>
@@ -8445,7 +8427,7 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D356" s="22" t="s">
+      <c r="D356" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E356" t="s">
@@ -8454,7 +8436,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B357" t="s">
         <v>6</v>
@@ -8472,7 +8454,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B358" t="s">
         <v>20</v>
@@ -8482,12 +8464,12 @@
         <v>Shared Center</v>
       </c>
       <c r="D358" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B359" t="s">
         <v>20</v>
@@ -8496,13 +8478,13 @@
         <f t="shared" si="5"/>
         <v>Shared Center</v>
       </c>
-      <c r="D359" s="18" t="s">
+      <c r="D359" s="17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B360" s="4" t="s">
         <v>20</v>
@@ -8520,7 +8502,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B361" t="s">
         <v>34</v>
@@ -8529,7 +8511,7 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D361" s="22" t="s">
+      <c r="D361" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E361" t="s">
@@ -8538,7 +8520,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B362" t="s">
         <v>34</v>
@@ -8547,16 +8529,16 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D362" s="22" t="s">
+      <c r="D362" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E362" s="23" t="s">
+      <c r="E362" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B363" t="s">
         <v>20</v>
@@ -8574,7 +8556,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B364" t="s">
         <v>25</v>
@@ -8583,13 +8565,13 @@
         <f t="shared" si="5"/>
         <v>EU/UK</v>
       </c>
-      <c r="D364" s="22" t="s">
+      <c r="D364" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B365" t="s">
         <v>10</v>
@@ -8598,13 +8580,13 @@
         <f t="shared" si="5"/>
         <v>Americas</v>
       </c>
-      <c r="D365" s="22" t="s">
-        <v>190</v>
+      <c r="D365" s="5" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B366" t="s">
         <v>6</v>
@@ -8613,13 +8595,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D366" s="22" t="s">
+      <c r="D366" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B367" t="s">
         <v>10</v>
@@ -8628,13 +8610,13 @@
         <f t="shared" si="5"/>
         <v>Americas</v>
       </c>
-      <c r="D367" s="22" t="s">
-        <v>190</v>
+      <c r="D367" s="5" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B368" t="s">
         <v>38</v>
@@ -8643,13 +8625,13 @@
         <f t="shared" si="5"/>
         <v>SME</v>
       </c>
-      <c r="D368" s="22" t="s">
-        <v>476</v>
+      <c r="D368" s="21" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B369" t="s">
         <v>6</v>
@@ -8658,13 +8640,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D369" s="22" t="s">
+      <c r="D369" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B370" t="s">
         <v>6</v>
@@ -8673,13 +8655,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D370" s="22" t="s">
+      <c r="D370" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B371" t="s">
         <v>38</v>
@@ -8689,12 +8671,12 @@
         <v>SME</v>
       </c>
       <c r="D371" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B372" t="s">
         <v>25</v>
@@ -8703,13 +8685,13 @@
         <f t="shared" si="5"/>
         <v>EU/UK</v>
       </c>
-      <c r="D372" s="24" t="s">
+      <c r="D372" s="23" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B373" t="s">
         <v>34</v>
@@ -8718,7 +8700,7 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D373" s="22" t="s">
+      <c r="D373" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E373" t="s">
@@ -8727,7 +8709,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B374" t="s">
         <v>25</v>
@@ -8736,13 +8718,13 @@
         <f t="shared" si="5"/>
         <v>EU/UK</v>
       </c>
-      <c r="D374" s="22" t="s">
+      <c r="D374" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B375" t="s">
         <v>6</v>
@@ -8757,7 +8739,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B376" t="s">
         <v>6</v>
@@ -8767,15 +8749,15 @@
         <v>APAC</v>
       </c>
       <c r="D376" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E376" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B377" t="s">
         <v>6</v>
@@ -8790,7 +8772,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B378" t="s">
         <v>25</v>
@@ -8799,13 +8781,13 @@
         <f t="shared" si="5"/>
         <v>EU/UK</v>
       </c>
-      <c r="D378" s="22" t="s">
+      <c r="D378" s="21" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B379" t="s">
         <v>6</v>
@@ -8814,13 +8796,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D379" s="22" t="s">
+      <c r="D379" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B380" t="s">
         <v>6</v>
@@ -8829,13 +8811,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D380" s="22" t="s">
+      <c r="D380" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B381" t="s">
         <v>6</v>
@@ -8850,7 +8832,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B382" t="s">
         <v>6</v>
@@ -8859,13 +8841,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D382" s="22" t="s">
+      <c r="D382" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B383" t="s">
         <v>34</v>
@@ -8874,7 +8856,7 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D383" s="24" t="s">
+      <c r="D383" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E383" t="s">
@@ -8883,7 +8865,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B384" t="s">
         <v>34</v>
@@ -8892,7 +8874,7 @@
         <f t="shared" si="5"/>
         <v>MEA</v>
       </c>
-      <c r="D384" s="24" t="s">
+      <c r="D384" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E384" t="s">
@@ -8901,7 +8883,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B385" t="s">
         <v>6</v>
@@ -8910,13 +8892,13 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D385" s="24" t="s">
+      <c r="D385" s="23" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B386" t="s">
         <v>20</v>
@@ -8926,12 +8908,12 @@
         <v>Shared Center</v>
       </c>
       <c r="D386" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B387" t="s">
         <v>10</v>
@@ -8940,13 +8922,13 @@
         <f t="shared" ref="C387:C434" si="6">B387</f>
         <v>Americas</v>
       </c>
-      <c r="D387" s="22" t="s">
+      <c r="D387" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B388" t="s">
         <v>10</v>
@@ -8955,8 +8937,8 @@
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D388" s="22" t="s">
-        <v>476</v>
+      <c r="D388" s="21" t="s">
+        <v>473</v>
       </c>
       <c r="E388" t="s">
         <v>58</v>
@@ -8964,7 +8946,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B389" t="s">
         <v>10</v>
@@ -8973,13 +8955,13 @@
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D389" s="22" t="s">
-        <v>476</v>
+      <c r="D389" s="21" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B390" t="s">
         <v>6</v>
@@ -8997,7 +8979,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B391" t="s">
         <v>25</v>
@@ -9006,13 +8988,13 @@
         <f t="shared" si="6"/>
         <v>EU/UK</v>
       </c>
-      <c r="D391" s="22" t="s">
+      <c r="D391" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B392" t="s">
         <v>38</v>
@@ -9022,12 +9004,12 @@
         <v>SME</v>
       </c>
       <c r="D392" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B393" t="s">
         <v>10</v>
@@ -9036,8 +9018,8 @@
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D393" s="22" t="s">
-        <v>476</v>
+      <c r="D393" s="21" t="s">
+        <v>473</v>
       </c>
       <c r="E393" t="s">
         <v>58</v>
@@ -9045,7 +9027,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B394" t="s">
         <v>10</v>
@@ -9054,8 +9036,8 @@
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D394" s="22" t="s">
-        <v>476</v>
+      <c r="D394" s="21" t="s">
+        <v>473</v>
       </c>
       <c r="E394" t="s">
         <v>58</v>
@@ -9063,7 +9045,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B395" t="s">
         <v>6</v>
@@ -9073,7 +9055,7 @@
         <v>APAC</v>
       </c>
       <c r="D395" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E395" s="5" t="s">
         <v>8</v>
@@ -9081,7 +9063,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B396" t="s">
         <v>34</v>
@@ -9090,16 +9072,16 @@
         <f t="shared" si="6"/>
         <v>MEA</v>
       </c>
-      <c r="D396" s="22" t="s">
+      <c r="D396" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E396" s="23" t="s">
+      <c r="E396" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B397" t="s">
         <v>6</v>
@@ -9117,7 +9099,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B398" t="s">
         <v>10</v>
@@ -9126,8 +9108,8 @@
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D398" s="22" t="s">
-        <v>476</v>
+      <c r="D398" s="21" t="s">
+        <v>473</v>
       </c>
       <c r="E398" t="s">
         <v>58</v>
@@ -9135,7 +9117,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B399" t="s">
         <v>6</v>
@@ -9145,7 +9127,7 @@
         <v>APAC</v>
       </c>
       <c r="D399" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E399" s="5" t="s">
         <v>8</v>
@@ -9153,7 +9135,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B400" t="s">
         <v>6</v>
@@ -9162,13 +9144,13 @@
         <f t="shared" si="6"/>
         <v>APAC</v>
       </c>
-      <c r="D400" s="22" t="s">
-        <v>81</v>
+      <c r="D400" s="21" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B401" t="s">
         <v>6</v>
@@ -9183,7 +9165,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B402" t="s">
         <v>10</v>
@@ -9192,8 +9174,8 @@
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D402" s="22" t="s">
-        <v>476</v>
+      <c r="D402" s="21" t="s">
+        <v>473</v>
       </c>
       <c r="E402" t="s">
         <v>58</v>
@@ -9201,7 +9183,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B403" t="s">
         <v>34</v>
@@ -9210,7 +9192,7 @@
         <f t="shared" si="6"/>
         <v>MEA</v>
       </c>
-      <c r="D403" s="22" t="s">
+      <c r="D403" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E403" t="s">
@@ -9219,7 +9201,7 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B404" t="s">
         <v>6</v>
@@ -9237,7 +9219,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B405" s="4" t="s">
         <v>25</v>
@@ -9247,15 +9229,15 @@
         <v>EU/UK</v>
       </c>
       <c r="D405" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E405" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B406" t="s">
         <v>25</v>
@@ -9264,13 +9246,13 @@
         <f t="shared" si="6"/>
         <v>EU/UK</v>
       </c>
-      <c r="D406" s="22" t="s">
+      <c r="D406" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B407" t="s">
         <v>10</v>
@@ -9279,13 +9261,13 @@
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D407" s="22" t="s">
-        <v>476</v>
+      <c r="D407" s="21" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B408" t="s">
         <v>25</v>
@@ -9294,13 +9276,13 @@
         <f t="shared" si="6"/>
         <v>EU/UK</v>
       </c>
-      <c r="D408" s="22" t="s">
+      <c r="D408" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B409" t="s">
         <v>6</v>
@@ -9318,7 +9300,7 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B410" t="s">
         <v>10</v>
@@ -9333,7 +9315,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B411" t="s">
         <v>34</v>
@@ -9342,7 +9324,7 @@
         <f t="shared" si="6"/>
         <v>MEA</v>
       </c>
-      <c r="D411" s="22" t="s">
+      <c r="D411" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E411" t="s">
@@ -9351,7 +9333,7 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B412" s="4" t="s">
         <v>25</v>
@@ -9366,7 +9348,7 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B413" t="s">
         <v>6</v>
@@ -9384,7 +9366,7 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B414" t="s">
         <v>6</v>
@@ -9402,7 +9384,7 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B415" t="s">
         <v>6</v>
@@ -9412,12 +9394,12 @@
         <v>APAC</v>
       </c>
       <c r="D415" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B416" t="s">
         <v>6</v>
@@ -9432,7 +9414,7 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B417" t="s">
         <v>34</v>
@@ -9441,8 +9423,8 @@
         <f t="shared" si="6"/>
         <v>MEA</v>
       </c>
-      <c r="D417" t="s">
-        <v>479</v>
+      <c r="D417" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -9450,7 +9432,7 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B418" t="s">
         <v>10</v>
@@ -9465,7 +9447,7 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B419" t="s">
         <v>6</v>
@@ -9483,7 +9465,7 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B420" t="s">
         <v>6</v>
@@ -9501,7 +9483,7 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B421" t="s">
         <v>6</v>
@@ -9519,7 +9501,7 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B422" t="s">
         <v>38</v>
@@ -9529,12 +9511,12 @@
         <v>SME</v>
       </c>
       <c r="D422" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B423" t="s">
         <v>6</v>
@@ -9549,7 +9531,7 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B424" t="s">
         <v>25</v>
@@ -9558,13 +9540,13 @@
         <f t="shared" si="6"/>
         <v>EU/UK</v>
       </c>
-      <c r="D424" s="22" t="s">
+      <c r="D424" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B425" t="s">
         <v>20</v>
@@ -9573,13 +9555,13 @@
         <f t="shared" si="6"/>
         <v>Shared Center</v>
       </c>
-      <c r="D425" s="18" t="s">
+      <c r="D425" s="17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B426" t="s">
         <v>38</v>
@@ -9589,12 +9571,12 @@
         <v>SME</v>
       </c>
       <c r="D426" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B427" t="s">
         <v>10</v>
@@ -9609,7 +9591,7 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B428" t="s">
         <v>38</v>
@@ -9619,12 +9601,12 @@
         <v>SME</v>
       </c>
       <c r="D428" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B429" t="s">
         <v>10</v>
@@ -9639,7 +9621,7 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B430" t="s">
         <v>20</v>
@@ -9649,12 +9631,12 @@
         <v>Shared Center</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B431" t="s">
         <v>25</v>
@@ -9663,16 +9645,16 @@
         <f t="shared" si="6"/>
         <v>EU/UK</v>
       </c>
-      <c r="D431" s="22" t="s">
+      <c r="D431" s="21" t="s">
         <v>11</v>
       </c>
       <c r="E431" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A432" s="26" t="s">
-        <v>482</v>
+      <c r="A432" s="25" t="s">
+        <v>478</v>
       </c>
       <c r="B432" s="4" t="s">
         <v>10</v>
@@ -9681,26 +9663,26 @@
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D432" s="6" t="s">
-        <v>190</v>
+      <c r="D432" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E432" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A433" s="26" t="s">
-        <v>483</v>
+      <c r="A433" s="25" t="s">
+        <v>479</v>
       </c>
       <c r="B433" t="s">
         <v>6</v>
       </c>
-      <c r="C433" s="27" t="str">
+      <c r="C433" s="26" t="str">
         <f t="shared" si="6"/>
         <v>APAC</v>
       </c>
-      <c r="D433" s="28" t="s">
-        <v>476</v>
+      <c r="D433" s="27" t="s">
+        <v>473</v>
       </c>
       <c r="E433" t="s">
         <v>36</v>
@@ -9708,25 +9690,25 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B434" t="s">
         <v>34</v>
       </c>
-      <c r="C434" s="29" t="str">
+      <c r="C434" s="26" t="str">
         <f t="shared" si="6"/>
         <v>MEA</v>
       </c>
-      <c r="D434" s="30" t="s">
-        <v>476</v>
-      </c>
-      <c r="E434" s="31" t="s">
-        <v>488</v>
+      <c r="D434" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="E434" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B435" t="s">
         <v>10</v>
@@ -9743,7 +9725,7 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B436" t="s">
         <v>34</v>
@@ -9751,7 +9733,7 @@
       <c r="C436" t="s">
         <v>34</v>
       </c>
-      <c r="D436" t="s">
+      <c r="D436" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E436" t="s">
@@ -9760,7 +9742,7 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B437" t="s">
         <v>6</v>
@@ -9769,14 +9751,14 @@
         <v>6</v>
       </c>
       <c r="D437" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E437" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E431" xr:uid="{0576E467-0835-47AC-A23C-AF9DB748328C}"/>
+  <autoFilter ref="A1:E437" xr:uid="{0576E467-0835-47AC-A23C-AF9DB748328C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://instarempte-my.sharepoint.com/personal/hetal_jethva_nium_com/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{C18877E2-DDA2-4646-872A-AC2AEC73D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47FC1F49-75A1-42EC-AD42-B59A7ED92C2B}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{C18877E2-DDA2-4646-872A-AC2AEC73D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE66A13-1A60-478F-BCDA-C420FE84D26B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A07144B-59AD-4B98-9627-376AA969DDF8}"/>
   </bookViews>
@@ -6621,7 +6621,7 @@
         <f t="shared" si="3"/>
         <v>APAC</v>
       </c>
-      <c r="D254" s="6" t="s">
+      <c r="D254" s="5" t="s">
         <v>125</v>
       </c>
       <c r="E254" t="s">
@@ -7197,7 +7197,7 @@
         <f t="shared" si="4"/>
         <v>APAC</v>
       </c>
-      <c r="D286" s="6" t="s">
+      <c r="D286" s="5" t="s">
         <v>125</v>
       </c>
       <c r="E286" t="s">
@@ -8748,8 +8748,8 @@
         <f t="shared" si="5"/>
         <v>APAC</v>
       </c>
-      <c r="D376" t="s">
-        <v>475</v>
+      <c r="D376" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="E376" t="s">
         <v>475</v>
@@ -9750,8 +9750,8 @@
       <c r="C437" t="s">
         <v>6</v>
       </c>
-      <c r="D437" t="s">
-        <v>475</v>
+      <c r="D437" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="E437" t="s">
         <v>475</v>

--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://instarempte-my.sharepoint.com/personal/hetal_jethva_nium_com/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{C18877E2-DDA2-4646-872A-AC2AEC73D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE66A13-1A60-478F-BCDA-C420FE84D26B}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{C18877E2-DDA2-4646-872A-AC2AEC73D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CDA71A8-A4AE-4E07-A5D3-49B9DDEE37F1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A07144B-59AD-4B98-9627-376AA969DDF8}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="486">
   <si>
     <t>Customer Label</t>
   </si>
@@ -1497,13 +1497,16 @@
   </si>
   <si>
     <t>Marek Pasik</t>
+  </si>
+  <si>
+    <t>Revelo Talent Corp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1562,12 +1565,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="6"/>
-      <color rgb="FF1E293B"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1589,7 +1586,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1623,15 +1620,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1639,7 +1627,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1709,11 +1697,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2051,7 +2034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0576E467-0835-47AC-A23C-AF9DB748328C}">
-  <dimension ref="A1:E437"/>
+  <dimension ref="A1:E438"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="1"/>
@@ -9653,35 +9636,35 @@
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A432" s="25" t="s">
+      <c r="A432" t="s">
         <v>478</v>
       </c>
-      <c r="B432" s="4" t="s">
+      <c r="B432" t="s">
         <v>10</v>
       </c>
       <c r="C432" s="4" t="str">
         <f t="shared" si="6"/>
         <v>Americas</v>
       </c>
-      <c r="D432" s="5" t="s">
+      <c r="D432" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="E432" s="6" t="s">
+      <c r="E432" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A433" s="25" t="s">
+      <c r="A433" t="s">
         <v>479</v>
       </c>
       <c r="B433" t="s">
         <v>6</v>
       </c>
-      <c r="C433" s="26" t="str">
+      <c r="C433" s="4" t="str">
         <f t="shared" si="6"/>
         <v>APAC</v>
       </c>
-      <c r="D433" s="27" t="s">
+      <c r="D433" s="21" t="s">
         <v>473</v>
       </c>
       <c r="E433" t="s">
@@ -9695,11 +9678,11 @@
       <c r="B434" t="s">
         <v>34</v>
       </c>
-      <c r="C434" s="26" t="str">
+      <c r="C434" s="4" t="str">
         <f t="shared" si="6"/>
         <v>MEA</v>
       </c>
-      <c r="D434" s="27" t="s">
+      <c r="D434" s="21" t="s">
         <v>473</v>
       </c>
       <c r="E434" t="s">
@@ -9713,10 +9696,10 @@
       <c r="B435" t="s">
         <v>10</v>
       </c>
-      <c r="C435" t="s">
+      <c r="C435" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D435" t="s">
+      <c r="D435" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E435" t="s">
@@ -9730,10 +9713,10 @@
       <c r="B436" t="s">
         <v>34</v>
       </c>
-      <c r="C436" t="s">
+      <c r="C436" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D436" s="5" t="s">
+      <c r="D436" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E436" t="s">
@@ -9747,14 +9730,31 @@
       <c r="B437" t="s">
         <v>6</v>
       </c>
-      <c r="C437" t="s">
-        <v>6</v>
-      </c>
-      <c r="D437" s="5" t="s">
+      <c r="C437" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D437" s="21" t="s">
         <v>125</v>
       </c>
       <c r="E437" t="s">
         <v>475</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>485</v>
+      </c>
+      <c r="B438" t="s">
+        <v>20</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D438" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E438" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Mapping.xlsx
+++ b/Mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://instarempte-my.sharepoint.com/personal/hetal_jethva_nium_com/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HetalJethva\OneDrive - Instarem PTE Ltd\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{C18877E2-DDA2-4646-872A-AC2AEC73D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CDA71A8-A4AE-4E07-A5D3-49B9DDEE37F1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75E7572-D7C9-4A97-8BA4-E5A3DE8F040E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A07144B-59AD-4B98-9627-376AA969DDF8}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$439</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="487">
   <si>
     <t>Customer Label</t>
   </si>
@@ -1500,6 +1500,9 @@
   </si>
   <si>
     <t>Revelo Talent Corp</t>
+  </si>
+  <si>
+    <t>Ohceans Pte Ltd</t>
   </si>
 </sst>
 </file>
@@ -2034,7 +2037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0576E467-0835-47AC-A23C-AF9DB748328C}">
-  <dimension ref="A1:E438"/>
+  <dimension ref="A1:E439"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="1"/>
@@ -2057,7 +2060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -2075,7 +2078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -2093,7 +2096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -2111,7 +2114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -2129,7 +2132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -2147,7 +2150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -2165,7 +2168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -2201,7 +2204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>24</v>
       </c>
@@ -9757,8 +9760,25 @@
         <v>8</v>
       </c>
     </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>486</v>
+      </c>
+      <c r="B439" t="s">
+        <v>20</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D439" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E439" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E437" xr:uid="{0576E467-0835-47AC-A23C-AF9DB748328C}"/>
+  <autoFilter ref="A1:E439" xr:uid="{0576E467-0835-47AC-A23C-AF9DB748328C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>